--- a/docs/test-cases/SPM-62_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-62_Test_Cases.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1354,8 +1354,38 @@
       </c>
       <c r="F33" s="9" t="n"/>
     </row>
+    <row r="35" ht="206.5" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Code reviewed</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>src/app/events/[id]/update/page.tsx
+src/app/events/[id]/page.tsx
+src/app/events/[id]/equipment/page.tsx
+src/app/api/events/[id]/information/route.ts
+src/app/api/events/[id]/equipment/route.ts
+src/app/api/events/[id]/equipment/[requestId]/route.ts
+src/lib/eventChangeImpact.ts
+src/lib/applyEventInformation.ts
+src/lib/eventInformationForm.ts
+src/lib/beginPlanning.ts
+src/lib/permissions.ts
+src/lib/validation/events.ts
+prisma/schema.prisma
+prisma/migrations/20261005120000_add_event_change_review_flags/migration.sql
+scripts/seed-spm62.ts</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E30:F30"/>
@@ -1373,6 +1403,7 @@
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -3093,13 +3124,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="58" customHeight="1">
+    <row r="2" ht="71.5" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-05). Every label, message, page address and rule below marked DECIDED was chosen here, in the style of the existing screens, and is what the developer now builds to. Change any of them before the code is written and update the cases with it.</t>
+          <t>Written before the code (TDD, 2026-10-05), then checked against the built screens the same day: every label, message and page address in the cases is what the code shows. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -3170,13 +3201,13 @@
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="355" customHeight="1">
+    <row r="9" ht="395.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Fixture events, to build as `scripts/seed-spm62.ts` (`npm run fixtures:spm62`) and to append to prisma/seed.ts once the review-flag columns exist. All are coordinated by Daniel Tan, and each has a unique title. (1) 'SPM62 Harbour Leadership Summit': Planning, organiser Evelyn Chen, 17 Mar 2027 09:00–17:00, attendance 80, layout theatre, required 'Fixed ceiling projector', Approved booking Orchard Seminar Room (ORC-SEM), 4K Portable Projector × 2 Reserved, registration on with capacity 100, closing 10 Mar 2027 18:00, and 12 attendees registered. (2) 'SPM62 Kirana Supplier Day': Planning, organiser Faridah Aziz, 21 Apr 2027 10:00–16:00, attendance 60, Approved booking Changi Conference Centre (CBP-CONF), Handheld Wireless Mic × 4 Reserved, registration on with 8 registered. (3) 'SPM62 Bayu Energy Outlook': Approved, organiser Hakim Zulkifli, 12 May 2027 09:00–12:00, attendance 40, no arrangements, registration off. (4) 'SPM62 Anchorpoint Logistics Forum': Approved, organiser Melissa Yap, 18 May 2027 09:00–12:00, attendance 50, no arrangements. (5) 'SPM62 Straits Pharmacy Forum': Confirmed, organiser Evelyn Chen, 9 Jun 2027 09:00–17:00, attendance 120, Approved booking Marina Auditorium (MAR-AUD), Powered Speaker × 2 Reserved, registration on with capacity 150 and 20 registered. (6) 'SPM62 Meridian Quarterly Review': Confirmed, organiser James Koh, 16 Jun 2027 14:00–17:00, attendance 30, Approved booking Marina Boardroom 1 (MAR-BR1), registration off. (7) 'SPM62 Sundara Hospitality Showcase': Confirmed, organiser Dewi Kartika, 23 Jun 2027 10:00–18:00, attendance 70, Approved booking Orchard Gallery (ORC-GAL), no equipment. (8) 'SPM62 Civic Learning Day': Under review, organiser Grace Abdullah, 7 Jul 2027. (9) 'SPM62 Pearl Delta Plant Tour': Completed, organiser Samuel Ong, 10 Sep 2026.</t>
+          <t>Fixture events: `scripts/seed-spm62.ts` (`npm run fixtures:spm62`) creates them with their bookings, equipment, registrations and required facility; prisma/seed.ts creates the same events only (appended last), so run the script once after a full reseed. All are coordinated by Daniel Tan, and each has a unique title. (1) 'SPM62 Harbour Leadership Summit': Planning, organiser Evelyn Chen, 17 Mar 2027 09:00–17:00, attendance 80, layout theatre, required 'Fixed ceiling projector', Approved booking Orchard Seminar Room (ORC-SEM), 4K Portable Projector × 2 Reserved, registration on with capacity 100, closing 15 Mar 2027 09:00 (two days before, as every seeded event's registration does), and 12 attendees registered. (2) 'SPM62 Kirana Supplier Day': Planning, organiser Faridah Aziz, 21 Apr 2027 10:00–16:00, attendance 60, Approved booking Changi Conference Centre (CBP-CONF), Handheld Wireless Mic × 4 Reserved, registration on with 8 registered. (3) 'SPM62 Bayu Energy Outlook': Approved, organiser Hakim Zulkifli, 12 May 2027 09:00–12:00, attendance 40, no arrangements, registration off. (4) 'SPM62 Anchorpoint Logistics Forum': Approved, organiser Melissa Yap, 18 May 2027 09:00–12:00, attendance 50, no arrangements. (5) 'SPM62 Straits Pharmacy Forum': Confirmed, organiser Evelyn Chen, 9 Jun 2027 09:00–17:00, attendance 120, Approved booking Marina Auditorium (MAR-AUD), Powered Speaker × 2 Reserved, registration on with capacity 150 and 20 registered. (6) 'SPM62 Meridian Quarterly Review': Confirmed, organiser James Koh, 16 Jun 2027 14:00–17:00, attendance 30, Approved booking Marina Boardroom 1 (MAR-BR1), registration off. (7) 'SPM62 Sundara Hospitality Showcase': Confirmed, organiser Dewi Kartika, 23 Jun 2027 10:00–18:00, attendance 70, Approved booking Orchard Gallery (ORC-GAL), no equipment. (8) 'SPM62 Civic Learning Day': Under review, organiser Grace Abdullah, 7 Jul 2027. (9) 'SPM62 Pearl Delta Plant Tour': Completed, organiser Samuel Ong, 10 Sep 2026.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
@@ -3575,8 +3606,8 @@
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Click 'Edit event information'
-3. Change 'Starts at' to 10 Mar 2027, 09:00
-4. Change 'Ends at' to 10 Mar 2027, 17:00
+3. Change 'Starts at' to 14 Mar 2027, 09:00
+4. Change 'Ends at' to 14 Mar 2027, 17:00
 5. Click 'Save changes'
 6. Click 'Cancel'</t>
         </is>
@@ -3590,7 +3621,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM62 Harbour Leadership Summit | Registration closes: 10 Mar 2027, 18:00 | Proposed: 10 Mar 2027, 09:00–17:00</t>
+          <t>Event: SPM62 Harbour Leadership Summit | Registration closes: 15 Mar 2027, 09:00 | Proposed: 14 Mar 2027, 09:00–17:00</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-62_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-62_Test_Cases.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Written before the code (TDD, 2026-10-05), then checked against the built screens the same day: every label, message and page address in the cases is what the code shows. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+          <t>Written before the code (TDD, 2026-10-05), then walked through the running app on 2026-10-05 (all 20 cases, against the SPM62 fixtures): every label, message and page address in the cases is what the code shows. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="85" customHeight="1">
+    <row r="6" ht="125.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'.
+          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time', because Ends at was changed.
 Step 6: The event page shows the title 'SPM62 Harbour Leadership Summit' and 'When' '17 Mar 2027, 09:00–17:00'.</t>
         </is>
       </c>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3467,8 +3467,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'.
-Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'.
+          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
+Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
 Step 7: The event page shows 'Expected attendance' '80'.</t>
         </is>
       </c>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 5: Nothing is saved and no dialog appears. 'Registration closes after this start time. Change the registration period first.' is shown in red under 'Starts at'.
+          <t>Step 5: Nothing is saved and no dialog appears. 'Registration closes after this start time. Change the registration period first.' is shown in red under 'Starts at'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time'.
 Step 6: The event page shows 'When' '17 Mar 2027, 09:00–17:00'.</t>
         </is>
       </c>

--- a/docs/test-cases/SPM-62_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-62_Test_Cases.xlsx
@@ -4,26 +4,27 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="TC16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="TC17" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="TC18" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="TC19" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="TC20" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TC18" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TC19" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TC20" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -192,6 +193,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,12 +490,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-62: As an authorised Event Coordinator, I want to update permitted event information so that event details remain accurate during planning</t>
         </is>
@@ -500,32 +507,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -552,27 +559,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC01</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>The edit form opens with the event's current information and only the fields a coordinator may change</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -591,27 +598,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC02</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>The form says when a change affects existing arrangements, naming the kind of change</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC4, AC7</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -630,27 +637,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC03</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>An ordinary edit to an Approved event is saved and shown on the event, with nothing flagged</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2, AC7</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -669,27 +676,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC04</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>A date and attendance change on an event with no arrangements is saved with nothing flagged</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC2, AC5</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -708,27 +715,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC05</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>A date change on a Planning event flags its venue booking, equipment and registrations without changing them</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC2, AC4, AC5</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -747,27 +754,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC06</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>The organiser sees the event's new date</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -786,27 +793,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC07</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>An attendance and venue requirement change flags only the venue booking</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC4, AC5</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -825,27 +832,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC08</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>On a Confirmed event, an important change asks first, and 'Keep editing' saves nothing</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -864,27 +871,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC09</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>A date change on a Confirmed event moves it back to Planning and flags its arrangements</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>AC2, AC5, AC6</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -903,27 +910,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC10</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>An ordinary edit to a Confirmed event keeps it Confirmed, with nothing flagged</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2, AC7</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -942,27 +949,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC11</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>The organiser sees an ordinary edit to their Confirmed event</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>AC2, AC7</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -981,27 +988,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC12</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>An important value changed and then changed back counts as an ordinary edit</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>AC4, AC7</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1020,27 +1027,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC13</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Adding equipment to a Confirmed event asks first, then moves it back to Planning</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>AC4, AC6</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1059,27 +1066,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC14</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>The event's organiser cannot edit its information</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1098,27 +1105,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC15</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>A coordinator who is not assigned to the event cannot edit its information</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1137,27 +1144,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC16</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>The Operations Manager cannot edit an event's information</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1176,27 +1183,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC17</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>The assigned coordinator cannot edit an event that is Under review or Completed</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1215,27 +1222,27 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC18</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>The event name can't be cleared and the end can't be before the start</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1254,27 +1261,27 @@
           <t>TC19</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC19</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Expected attendance can't be blank or below 1</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1293,27 +1300,27 @@
           <t>TC20</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC20</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>The event can't be moved to start before its registration closes</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1329,19 +1336,19 @@
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C26" s="20" t="n"/>
       <c r="D26" s="21" t="n"/>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1349,19 +1356,19 @@
       <c r="F26" s="21" t="n"/>
     </row>
     <row r="27" ht="84.75" customHeight="1" s="19">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>Authorised users can update permitted event information.</t>
         </is>
       </c>
       <c r="C27" s="20" t="n"/>
       <c r="D27" s="21" t="n"/>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC01
 SPM-62-TC03
@@ -1374,19 +1381,19 @@
       <c r="F27" s="21" t="n"/>
     </row>
     <row r="28" ht="98.25" customHeight="1" s="19">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Changes are reflected in the event record.</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="21" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC03
 SPM-62-TC04
@@ -1400,19 +1407,19 @@
       <c r="F28" s="21" t="n"/>
     </row>
     <row r="29" ht="71.25" customHeight="1" s="19">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Users cannot edit information they are not authorised to modify.</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="21" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC01
 SPM-62-TC14
@@ -1424,19 +1431,19 @@
       <c r="F29" s="21" t="n"/>
     </row>
     <row r="30" ht="71.25" customHeight="1" s="19">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Important information such as date, time, attendance, venue and equipment requirements is identified as affecting existing arrangements.</t>
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="21" t="n"/>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC02
 SPM-62-TC05
@@ -1448,19 +1455,19 @@
       <c r="F30" s="21" t="n"/>
     </row>
     <row r="31" ht="57.75" customHeight="1" s="19">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Given important information is changed on an event with existing venue, equipment or registration arrangements, when the change is saved, then the affected arrangements are identified and flagged for review rather than automatically changed.</t>
         </is>
       </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="21" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC04
 SPM-62-TC05
@@ -1471,19 +1478,19 @@
       <c r="F31" s="21" t="n"/>
     </row>
     <row r="32" ht="71.25" customHeight="1" s="19">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>Given the event is Confirmed and the change affects its essential arrangements, when the change is saved, then the event status reverts (e.g. to Planning) so it can be reconfirmed. Notifying the Event Organiser that it is no longer confirmed is covered by Receive Event Notifications (SPM-53).</t>
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="21" t="n"/>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC08
 SPM-62-TC09
@@ -1493,19 +1500,19 @@
       <c r="F32" s="21" t="n"/>
     </row>
     <row r="33" ht="71.25" customHeight="1" s="19">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>An ordinary edit that does not affect existing arrangements does not flag arrangements or change the event status.</t>
         </is>
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="21" t="n"/>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>SPM-62-TC02
 SPM-62-TC03
@@ -1518,12 +1525,12 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" s="19"/>
     <row r="35" ht="206.25" customHeight="1" s="19">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>src/app/events/[id]/update/page.tsx
 src/app/events/[id]/page.tsx
@@ -2588,71 +2595,69 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="138.75" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Straits Pharmacy Forum' is back to Confirmed.
+'SPM62 Straits Pharmacy Forum' is Confirmed (if SPM-62-TC09 has been run since the last reset, run `npm run fixtures:spm62` first).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="125.25" customHeight="1" s="19">
+Nothing is saved in this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Straits Pharmacy Forum'
 2. Click 'Edit event information'
 3. Change 'Starts at' to 16 Jun 2027, 09:00
 4. Change 'Ends at' to 16 Jun 2027, 17:00
 5. Click 'Save changes'
-6. Click 'Save and move to Planning'
-7. Click 'Back to event'
-8. Click 'All Events' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
+6. Click 'Keep editing'
+7. Click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Straits Pharmacy Forum | Status: Confirmed | When: 9 Jun 2027, 09:00–17:00 -&gt; 16 Jun 2027, 09:00–17:00 | Approved booking: Marina Auditorium (MAR-AUD) | Equipment: Powered Speaker x 2, Reserved | Registrations: 20 attendees registered</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="260.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Straits Pharmacy Forum | Status: Confirmed | When: 9 Jun 2027, 09:00–17:00 | Proposed: 16 Jun 2027, 09:00–17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
-Step 5: The 'Move this event back to Planning?' dialog appears.
-Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
-Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
-Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
+Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
+Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2667,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2694,13 +2699,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
-Step 5: The 'Move this event back to Planning?' dialog appears.
-Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
-Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
-Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
+Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
+Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2738,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2764,13 +2768,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
-Step 5: The 'Move this event back to Planning?' dialog appears.
-Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
-Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
-Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
+Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
+Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2807,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -3833,24 +3836,24 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="179.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Meridian Quarterly Review' is back in its starting state.
+Before: run `npm run fixtures:spm62` so 'SPM62 Straits Pharmacy Forum' is back to Confirmed.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-After: if you are running SPM-62-TC11 next, go straight to it - it checks this edit as the organiser. Otherwise run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
         </is>
       </c>
     </row>
@@ -3860,14 +3863,16 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Straits Pharmacy Forum'
 2. Click 'Edit event information'
-3. Change 'Description' to 'Q3 results, Q4 forecast and open questions'
-4. Change 'Other accessibility notes' to 'Two attendees use wheelchairs'
+3. Change 'Starts at' to 16 Jun 2027, 09:00
+4. Change 'Ends at' to 16 Jun 2027, 17:00
 5. Click 'Save changes'
-6. Click 'Back to event'</t>
+6. Click 'Save and move to Planning'
+7. Click 'Back to event'
+8. Click 'All Events' in the sidebar</t>
         </is>
       </c>
     </row>
@@ -3877,24 +3882,25 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Meridian Quarterly Review | Status: Confirmed | Approved booking: Marina Boardroom 1 (MAR-BR1) | Description: Q3 results, Q4 forecast and open questions | Other accessibility notes: Two attendees use wheelchairs | Organiser: James Koh</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="152.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Straits Pharmacy Forum | Status: Confirmed | When: 9 Jun 2027, 09:00–17:00 -&gt; 16 Jun 2027, 09:00–17:00 | Approved booking: Marina Auditorium (MAR-AUD) | Equipment: Powered Speaker x 2, Reserved | Registrations: 20 attendees registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="260.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 4: No amber warning has appeared.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
+Step 5: The 'Move this event back to Planning?' dialog appears.
+Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
+Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
+Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3910,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3936,12 +3942,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 4: No amber warning has appeared.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
+Step 5: The 'Move this event back to Planning?' dialog appears.
+Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
+Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
+Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3982,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -4005,12 +4012,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 4: No amber warning has appeared.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, and there is no 'Confirm event' button.
+Step 5: The 'Move this event back to Planning?' dialog appears.
+Step 6: The dialog closes. The form is replaced by a green alert 'Event information updated. The event is back in Planning and needs to be confirmed again.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists: 'Venue booking: Marina Auditorium (MAR-AUD) – the date or time changed'; 'Equipment: Powered Speaker × 2 – the date or time changed'; 'Registrations: 20 attendees – the date or time changed'.
+Step 7: The event page shows the 'Planning' status badge, 'When' '16 Jun 2027, 09:00–17:00' and Status 'Planning' in the Details card, and a 'Confirm event' button at the top of the page.
+Step 8: The 'SPM62 Straits Pharmacy Forum' row shows 'Planning' in the Status column.</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4052,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -5073,59 +5081,68 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="111.75" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="179.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC10 has just been run ('SPM62 Meridian Quarterly Review' description and accessibility notes changed by Daniel Tan; still Confirmed).
-Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser of 'SPM62 Meridian Quarterly Review'.
-After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
+Before: run `npm run fixtures:spm62` so 'SPM62 Meridian Quarterly Review' is back in its starting state.
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+After: if you are running SPM-62-TC11 next, go straight to it - it checks this edit as the organiser. Otherwise run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'
+2. Click 'Edit event information'
+3. Change 'Description' to 'Q3 results, Q4 forecast and open questions'
+4. Change 'Other accessibility notes' to 'Two attendees use wheelchairs'
+5. Click 'Save changes'
+6. Click 'Back to event'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Meridian Quarterly Review | Organiser: James Koh</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Meridian Quarterly Review | Status: Confirmed | Approved booking: Marina Boardroom 1 (MAR-BR1) | Description: Q3 results, Q4 forecast and open questions | Other accessibility notes: Two attendees use wheelchairs | Organiser: James Koh</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 4: No amber warning has appeared.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5152,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5167,9 +5184,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 4: No amber warning has appeared.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5223,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5233,9 +5253,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 4: No amber warning has appeared.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 6: The status badge still reads 'Confirmed' and there is no 'Confirm event' button. The Details card shows Description 'Q3 results, Q4 forecast and open questions', the Venue requirements card shows Accessibility notes 'Two attendees use wheelchairs', and Venue still reads 'Marina Boardroom 1 (MAR-BR1)'.</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5292,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -6298,69 +6321,59 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="111.75" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Meridian Quarterly Review' is back in its starting state.
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC10 has just been run ('SPM62 Meridian Quarterly Review' description and accessibility notes changed by Daniel Tan; still Confirmed).
+Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser of 'SPM62 Meridian Quarterly Review'.
 After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="19">
+    <row r="4" ht="30.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'
-2. Click 'Edit event information'
-3. Change 'Expected attendance' to 45
-4. Change 'Expected attendance' back to 30
-5. Change 'Description' to 'Agenda: results, forecast and Q&amp;A'
-6. Click 'Save changes'
-7. Click 'Back to event'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Meridian Quarterly Review | Status: Confirmed | Expected attendance: 30 -&gt; 45 -&gt; 30 | Description: Agenda: results, forecast and Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="165.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Meridian Quarterly Review | Organiser: James Koh</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 4: The amber alert disappears.
-Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6383,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6402,12 +6415,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 4: The amber alert disappears.
-Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6451,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6471,12 +6481,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 4: The amber alert disappears.
-Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge, Description 'Q3 results, Q4 forecast and open questions' and Accessibility notes 'Two attendees use wheelchairs'.</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6517,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -7539,9 +7546,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC13</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC12</t>
         </is>
       </c>
     </row>
@@ -7551,32 +7558,30 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Sundara Hospitality Showcase' is back to Confirmed.
+Before: run `npm run fixtures:spm62` so 'SPM62 Meridian Quarterly Review' is back in its starting state.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
 After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="152.25" customHeight="1" s="19">
+    <row r="4" ht="125.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Sundara Hospitality Showcase'
-2. Click the 'Equipment' tab
-3. Choose 'Handheld Wireless Mic' in 'Equipment' under 'Add equipment'
-4. Enter 2 in 'Quantity'
-5. Click 'Add'
-6. Click 'Cancel' in the dialog
-7. Click 'Add'
-8. Click 'Continue' in the dialog
-9. Click the 'Overview' tab</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Meridian Quarterly Review'
+2. Click 'Edit event information'
+3. Change 'Expected attendance' to 45
+4. Change 'Expected attendance' back to 30
+5. Change 'Description' to 'Agenda: results, forecast and Q&amp;A'
+6. Click 'Save changes'
+7. Click 'Back to event'</t>
         </is>
       </c>
     </row>
@@ -7586,26 +7591,24 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Sundara Hospitality Showcase | Status: Confirmed | Approved booking: Orchard Gallery (ORC-GAL) | Added: Handheld Wireless Mic x 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="246.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Meridian Quarterly Review | Status: Confirmed | Expected attendance: 30 -&gt; 45 -&gt; 30 | Description: Agenda: results, forecast and Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="165.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
-Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
-Step 7: The same dialog appears again.
-Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
-Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 4: The amber alert disappears.
+Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7618,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7647,14 +7650,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
-Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
-Step 7: The same dialog appears again.
-Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
-Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 4: The amber alert disappears.
+Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7689,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7718,14 +7719,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
-Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
-Step 7: The same dialog appears again.
-Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
-Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: The amber alert appears, reading 'You've changed: Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 4: The amber alert disappears.
+Step 6: No 'Move this event back to Planning?' dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The status badge still reads 'Confirmed', 'Expected attendance' shows '30', and Description shows 'Agenda: results, forecast and Q&amp;A'.</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7758,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -8788,62 +8787,73 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="111.75" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), Event Organiser of 'SPM62 Harbour Leadership Summit'.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.25" customHeight="1" s="19">
+Before: run `npm run fixtures:spm62` so 'SPM62 Sundara Hospitality Showcase' is back to Confirmed.
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
-2. Note the event reference shown next to the title (it starts with EVT-)
-3. Type /events/&lt;reference from step 2&gt;/update after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 2&gt;/update) and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Sundara Hospitality Showcase'
+2. Click the 'Equipment' tab
+3. Choose 'Handheld Wireless Mic' in 'Equipment' under 'Add equipment'
+4. Enter 2 in 'Quantity'
+5. Click 'Add'
+6. Click 'Cancel' in the dialog
+7. Click 'Add'
+8. Click 'Continue' in the dialog
+9. Click the 'Overview' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Evelyn Chen, Event Organiser who raised the request</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Sundara Hospitality Showcase | Status: Confirmed | Approved booking: Orchard Gallery (ORC-GAL) | Added: Handheld Wireless Mic x 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="246.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
+Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
+Step 7: The same dialog appears again.
+Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
+Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8863,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8885,10 +8895,14 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
+Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
+Step 7: The same dialog appears again.
+Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
+Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8936,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8952,10 +8966,14 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Confirmed' status badge.
+Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Sundara Hospitality Showcase is Confirmed. Changing its equipment moves it back to Planning so it can be confirmed again.' with the buttons 'Cancel' and 'Continue'. Nothing has been added yet.
+Step 6: The dialog closes. 'Handheld Wireless Mic' is not in the list of requested items, and it is still chosen under 'Add equipment'.
+Step 7: The same dialog appears again.
+Step 8: The dialog closes. 'Handheld Wireless Mic', quantity 2, is listed with the 'Requested' badge. An amber alert 'This event is no longer confirmed' reads 'Changing its equipment moved it back to Planning so it can be confirmed again.' No 'Planning has started' alert is shown.
+Step 9: The event page shows the 'Planning' status badge, Status 'Planning' in the Details card, and a 'Confirm event' button.</t>
         </is>
       </c>
     </row>
@@ -8989,7 +9007,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -10018,9 +10036,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC15</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC14</t>
         </is>
       </c>
     </row>
@@ -10030,10 +10048,10 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Logged in as Priya Raj (priya.raj@connectsphere.com / password123), an Event Coordinator who is not assigned to any 'SPM62 …' event.
+Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), Event Organiser of 'SPM62 Harbour Leadership Summit'.
 Nothing is saved in this case.</t>
         </is>
       </c>
@@ -10044,9 +10062,9 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Note the event reference shown next to the title (it starts with EVT-)
 3. Type /events/&lt;reference from step 2&gt;/update after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 2&gt;/update) and press Enter</t>
         </is>
@@ -10058,9 +10076,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning, coordinator Daniel Tan) | User: Priya Raj, Event Coordinator</t>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Evelyn Chen, Event Organiser who raised the request</t>
         </is>
       </c>
     </row>
@@ -10070,9 +10088,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -10083,7 +10101,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10115,9 +10133,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -10152,7 +10170,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10182,9 +10200,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -10219,7 +10237,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -11248,22 +11266,22 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="111.75" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Logged in as Grace Lim (grace.lim@connectsphere.com / password123), Operations Manager.
+Logged in as Priya Raj (priya.raj@connectsphere.com / password123), an Event Coordinator who is not assigned to any 'SPM62 …' event.
 Nothing is saved in this case.</t>
         </is>
       </c>
@@ -11274,7 +11292,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Note the event reference shown next to the title (it starts with EVT-)
@@ -11288,9 +11306,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Grace Lim, Operations Manager</t>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning, coordinator Daniel Tan) | User: Priya Raj, Event Coordinator</t>
         </is>
       </c>
     </row>
@@ -11300,9 +11318,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -11313,7 +11331,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11345,9 +11363,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -11382,7 +11400,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11412,9 +11430,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the event with 'Daniel Tan' as Coordinator. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
@@ -11449,7 +11467,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -12478,9 +12496,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC17</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC16</t>
         </is>
       </c>
     </row>
@@ -12490,55 +12508,50 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+Logged in as Grace Lim (grace.lim@connectsphere.com / password123), Operations Manager.
 Nothing is saved in this case.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="179.25" customHeight="1" s="19">
+    <row r="4" ht="98.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Civic Learning Day'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Note the event reference shown next to the title (it starts with EVT-)
-3. Type /events/&lt;reference from step 2&gt;/update after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 2&gt;/update) and press Enter
-4. Click 'All Events' in the sidebar and open 'SPM62 Pearl Delta Plant Tour'
-5. Note the event reference shown next to the title (it starts with EVT-)
-6. Type /events/&lt;reference from step 5&gt;/update after the site address in the browser address bar and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="19">
+3. Type /events/&lt;reference from step 2&gt;/update after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 2&gt;/update) and press Enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Events: SPM62 Civic Learning Day (Under review) and SPM62 Pearl Delta Plant Tour (Completed), both assigned to Daniel Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="165.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Grace Lim, Operations Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
-Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
-Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12561,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12580,12 +12593,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
-Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
-Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12630,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12649,12 +12660,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
-Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
-Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
-Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12697,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -13717,9 +13726,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC18</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC17</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13738,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
@@ -13737,20 +13746,20 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="98.25" customHeight="1" s="19">
+    <row r="4" ht="179.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
-2. Click 'Edit event information'
-3. Clear 'Event name'
-4. Change 'Ends at' to 17 Mar 2027, 08:00
-5. Click 'Save changes'
-6. Click 'Cancel'</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Civic Learning Day'
+2. Note the event reference shown next to the title (it starts with EVT-)
+3. Type /events/&lt;reference from step 2&gt;/update after the site address in the browser address bar (e.g. http://localhost:3000/events/&lt;reference from step 2&gt;/update) and press Enter
+4. Click 'All Events' in the sidebar and open 'SPM62 Pearl Delta Plant Tour'
+5. Note the event reference shown next to the title (it starts with EVT-)
+6. Type /events/&lt;reference from step 5&gt;/update after the site address in the browser address bar and press Enter</t>
         </is>
       </c>
     </row>
@@ -13760,22 +13769,24 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit | Event name: (blank) | Starts at: 17 Mar 2027, 09:00 | Ends at: 17 Mar 2027, 08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="125.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Events: SPM62 Civic Learning Day (Under review) and SPM62 Pearl Delta Plant Tour (Completed), both assigned to Daniel Tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="165.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time', because Ends at was changed.
-Step 6: The event page shows the title 'SPM62 Harbour Leadership Summit' and 'When' '17 Mar 2027, 09:00–17:00'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
+Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
+Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -13785,7 +13796,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13817,10 +13828,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time', because Ends at was changed.
-Step 6: The event page shows the title 'SPM62 Harbour Leadership Summit' and 'When' '17 Mar 2027, 09:00–17:00'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
+Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
+Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -13854,7 +13867,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13884,14 +13897,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
-2. Click 'Edit event information'
-3. Clear 'Event name'
-4. Change 'Ends at' to 17 Mar 2027, 08:00
-5. Click 'Save changes'
-6. Click 'Cancel'</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' status badge. There is no 'Edit event information' button.
+Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' and a 'Back to event' button. No form fields are shown.
+Step 4: The event page shows the 'Completed' status badge. There is no 'Edit event information' button.
+Step 6: The same red alert is shown, reading 'Event information can only be changed while the event is Approved, Planning or Confirmed.' No form fields are shown.</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13936,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -14929,1233 +14940,124 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="19" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
+    <col width="5" customWidth="1" style="19" min="1" max="1"/>
+    <col width="75" customWidth="1" style="19" min="2" max="2"/>
+    <col width="40" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="19">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="19">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
-2. Click 'Edit event information'
-3. Click 'Cancel'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="19">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit | Status: Planning | When: 17 Mar 2027, 09:00–17:00 | Expected attendance: 80 | Layout: Theatre | Required facility: Fixed ceiling projector</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="206.25" customHeight="1" s="19">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
-Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
-Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="19">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>46300</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="15.75" customHeight="1" s="19">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
-Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
-Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="19">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="19">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="19">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>46300</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="19">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
-Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
-Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="19">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Kayal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="19">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="19"/>
-    <row r="23" ht="15.75" customHeight="1" s="19"/>
-    <row r="24" ht="15.75" customHeight="1" s="19"/>
-    <row r="25" ht="15.75" customHeight="1" s="19"/>
-    <row r="26" ht="15.75" customHeight="1" s="19"/>
-    <row r="27" ht="15.75" customHeight="1" s="19"/>
-    <row r="28" ht="15.75" customHeight="1" s="19"/>
-    <row r="29" ht="15.75" customHeight="1" s="19"/>
-    <row r="30" ht="15.75" customHeight="1" s="19"/>
-    <row r="31" ht="15.75" customHeight="1" s="19"/>
-    <row r="32" ht="15.75" customHeight="1" s="19"/>
-    <row r="33" ht="15.75" customHeight="1" s="19"/>
-    <row r="34" ht="15.75" customHeight="1" s="19"/>
-    <row r="35" ht="15.75" customHeight="1" s="19"/>
-    <row r="36" ht="15.75" customHeight="1" s="19"/>
-    <row r="37" ht="15.75" customHeight="1" s="19"/>
-    <row r="38" ht="15.75" customHeight="1" s="19"/>
-    <row r="39" ht="15.75" customHeight="1" s="19"/>
-    <row r="40" ht="15.75" customHeight="1" s="19"/>
-    <row r="41" ht="15.75" customHeight="1" s="19"/>
-    <row r="42" ht="15.75" customHeight="1" s="19"/>
-    <row r="43" ht="15.75" customHeight="1" s="19"/>
-    <row r="44" ht="15.75" customHeight="1" s="19"/>
-    <row r="45" ht="15.75" customHeight="1" s="19"/>
-    <row r="46" ht="15.75" customHeight="1" s="19"/>
-    <row r="47" ht="15.75" customHeight="1" s="19"/>
-    <row r="48" ht="15.75" customHeight="1" s="19"/>
-    <row r="49" ht="15.75" customHeight="1" s="19"/>
-    <row r="50" ht="15.75" customHeight="1" s="19"/>
-    <row r="51" ht="15.75" customHeight="1" s="19"/>
-    <row r="52" ht="15.75" customHeight="1" s="19"/>
-    <row r="53" ht="15.75" customHeight="1" s="19"/>
-    <row r="54" ht="15.75" customHeight="1" s="19"/>
-    <row r="55" ht="15.75" customHeight="1" s="19"/>
-    <row r="56" ht="15.75" customHeight="1" s="19"/>
-    <row r="57" ht="15.75" customHeight="1" s="19"/>
-    <row r="58" ht="15.75" customHeight="1" s="19"/>
-    <row r="59" ht="15.75" customHeight="1" s="19"/>
-    <row r="60" ht="15.75" customHeight="1" s="19"/>
-    <row r="61" ht="15.75" customHeight="1" s="19"/>
-    <row r="62" ht="15.75" customHeight="1" s="19"/>
-    <row r="63" ht="15.75" customHeight="1" s="19"/>
-    <row r="64" ht="15.75" customHeight="1" s="19"/>
-    <row r="65" ht="15.75" customHeight="1" s="19"/>
-    <row r="66" ht="15.75" customHeight="1" s="19"/>
-    <row r="67" ht="15.75" customHeight="1" s="19"/>
-    <row r="68" ht="15.75" customHeight="1" s="19"/>
-    <row r="69" ht="15.75" customHeight="1" s="19"/>
-    <row r="70" ht="15.75" customHeight="1" s="19"/>
-    <row r="71" ht="15.75" customHeight="1" s="19"/>
-    <row r="72" ht="15.75" customHeight="1" s="19"/>
-    <row r="73" ht="15.75" customHeight="1" s="19"/>
-    <row r="74" ht="15.75" customHeight="1" s="19"/>
-    <row r="75" ht="15.75" customHeight="1" s="19"/>
-    <row r="76" ht="15.75" customHeight="1" s="19"/>
-    <row r="77" ht="15.75" customHeight="1" s="19"/>
-    <row r="78" ht="15.75" customHeight="1" s="19"/>
-    <row r="79" ht="15.75" customHeight="1" s="19"/>
-    <row r="80" ht="15.75" customHeight="1" s="19"/>
-    <row r="81" ht="15.75" customHeight="1" s="19"/>
-    <row r="82" ht="15.75" customHeight="1" s="19"/>
-    <row r="83" ht="15.75" customHeight="1" s="19"/>
-    <row r="84" ht="15.75" customHeight="1" s="19"/>
-    <row r="85" ht="15.75" customHeight="1" s="19"/>
-    <row r="86" ht="15.75" customHeight="1" s="19"/>
-    <row r="87" ht="15.75" customHeight="1" s="19"/>
-    <row r="88" ht="15.75" customHeight="1" s="19"/>
-    <row r="89" ht="15.75" customHeight="1" s="19"/>
-    <row r="90" ht="15.75" customHeight="1" s="19"/>
-    <row r="91" ht="15.75" customHeight="1" s="19"/>
-    <row r="92" ht="15.75" customHeight="1" s="19"/>
-    <row r="93" ht="15.75" customHeight="1" s="19"/>
-    <row r="94" ht="15.75" customHeight="1" s="19"/>
-    <row r="95" ht="15.75" customHeight="1" s="19"/>
-    <row r="96" ht="15.75" customHeight="1" s="19"/>
-    <row r="97" ht="15.75" customHeight="1" s="19"/>
-    <row r="98" ht="15.75" customHeight="1" s="19"/>
-    <row r="99" ht="15.75" customHeight="1" s="19"/>
-    <row r="100" ht="15.75" customHeight="1" s="19"/>
-    <row r="101" ht="15.75" customHeight="1" s="19"/>
-    <row r="102" ht="15.75" customHeight="1" s="19"/>
-    <row r="103" ht="15.75" customHeight="1" s="19"/>
-    <row r="104" ht="15.75" customHeight="1" s="19"/>
-    <row r="105" ht="15.75" customHeight="1" s="19"/>
-    <row r="106" ht="15.75" customHeight="1" s="19"/>
-    <row r="107" ht="15.75" customHeight="1" s="19"/>
-    <row r="108" ht="15.75" customHeight="1" s="19"/>
-    <row r="109" ht="15.75" customHeight="1" s="19"/>
-    <row r="110" ht="15.75" customHeight="1" s="19"/>
-    <row r="111" ht="15.75" customHeight="1" s="19"/>
-    <row r="112" ht="15.75" customHeight="1" s="19"/>
-    <row r="113" ht="15.75" customHeight="1" s="19"/>
-    <row r="114" ht="15.75" customHeight="1" s="19"/>
-    <row r="115" ht="15.75" customHeight="1" s="19"/>
-    <row r="116" ht="15.75" customHeight="1" s="19"/>
-    <row r="117" ht="15.75" customHeight="1" s="19"/>
-    <row r="118" ht="15.75" customHeight="1" s="19"/>
-    <row r="119" ht="15.75" customHeight="1" s="19"/>
-    <row r="120" ht="15.75" customHeight="1" s="19"/>
-    <row r="121" ht="15.75" customHeight="1" s="19"/>
-    <row r="122" ht="15.75" customHeight="1" s="19"/>
-    <row r="123" ht="15.75" customHeight="1" s="19"/>
-    <row r="124" ht="15.75" customHeight="1" s="19"/>
-    <row r="125" ht="15.75" customHeight="1" s="19"/>
-    <row r="126" ht="15.75" customHeight="1" s="19"/>
-    <row r="127" ht="15.75" customHeight="1" s="19"/>
-    <row r="128" ht="15.75" customHeight="1" s="19"/>
-    <row r="129" ht="15.75" customHeight="1" s="19"/>
-    <row r="130" ht="15.75" customHeight="1" s="19"/>
-    <row r="131" ht="15.75" customHeight="1" s="19"/>
-    <row r="132" ht="15.75" customHeight="1" s="19"/>
-    <row r="133" ht="15.75" customHeight="1" s="19"/>
-    <row r="134" ht="15.75" customHeight="1" s="19"/>
-    <row r="135" ht="15.75" customHeight="1" s="19"/>
-    <row r="136" ht="15.75" customHeight="1" s="19"/>
-    <row r="137" ht="15.75" customHeight="1" s="19"/>
-    <row r="138" ht="15.75" customHeight="1" s="19"/>
-    <row r="139" ht="15.75" customHeight="1" s="19"/>
-    <row r="140" ht="15.75" customHeight="1" s="19"/>
-    <row r="141" ht="15.75" customHeight="1" s="19"/>
-    <row r="142" ht="15.75" customHeight="1" s="19"/>
-    <row r="143" ht="15.75" customHeight="1" s="19"/>
-    <row r="144" ht="15.75" customHeight="1" s="19"/>
-    <row r="145" ht="15.75" customHeight="1" s="19"/>
-    <row r="146" ht="15.75" customHeight="1" s="19"/>
-    <row r="147" ht="15.75" customHeight="1" s="19"/>
-    <row r="148" ht="15.75" customHeight="1" s="19"/>
-    <row r="149" ht="15.75" customHeight="1" s="19"/>
-    <row r="150" ht="15.75" customHeight="1" s="19"/>
-    <row r="151" ht="15.75" customHeight="1" s="19"/>
-    <row r="152" ht="15.75" customHeight="1" s="19"/>
-    <row r="153" ht="15.75" customHeight="1" s="19"/>
-    <row r="154" ht="15.75" customHeight="1" s="19"/>
-    <row r="155" ht="15.75" customHeight="1" s="19"/>
-    <row r="156" ht="15.75" customHeight="1" s="19"/>
-    <row r="157" ht="15.75" customHeight="1" s="19"/>
-    <row r="158" ht="15.75" customHeight="1" s="19"/>
-    <row r="159" ht="15.75" customHeight="1" s="19"/>
-    <row r="160" ht="15.75" customHeight="1" s="19"/>
-    <row r="161" ht="15.75" customHeight="1" s="19"/>
-    <row r="162" ht="15.75" customHeight="1" s="19"/>
-    <row r="163" ht="15.75" customHeight="1" s="19"/>
-    <row r="164" ht="15.75" customHeight="1" s="19"/>
-    <row r="165" ht="15.75" customHeight="1" s="19"/>
-    <row r="166" ht="15.75" customHeight="1" s="19"/>
-    <row r="167" ht="15.75" customHeight="1" s="19"/>
-    <row r="168" ht="15.75" customHeight="1" s="19"/>
-    <row r="169" ht="15.75" customHeight="1" s="19"/>
-    <row r="170" ht="15.75" customHeight="1" s="19"/>
-    <row r="171" ht="15.75" customHeight="1" s="19"/>
-    <row r="172" ht="15.75" customHeight="1" s="19"/>
-    <row r="173" ht="15.75" customHeight="1" s="19"/>
-    <row r="174" ht="15.75" customHeight="1" s="19"/>
-    <row r="175" ht="15.75" customHeight="1" s="19"/>
-    <row r="176" ht="15.75" customHeight="1" s="19"/>
-    <row r="177" ht="15.75" customHeight="1" s="19"/>
-    <row r="178" ht="15.75" customHeight="1" s="19"/>
-    <row r="179" ht="15.75" customHeight="1" s="19"/>
-    <row r="180" ht="15.75" customHeight="1" s="19"/>
-    <row r="181" ht="15.75" customHeight="1" s="19"/>
-    <row r="182" ht="15.75" customHeight="1" s="19"/>
-    <row r="183" ht="15.75" customHeight="1" s="19"/>
-    <row r="184" ht="15.75" customHeight="1" s="19"/>
-    <row r="185" ht="15.75" customHeight="1" s="19"/>
-    <row r="186" ht="15.75" customHeight="1" s="19"/>
-    <row r="187" ht="15.75" customHeight="1" s="19"/>
-    <row r="188" ht="15.75" customHeight="1" s="19"/>
-    <row r="189" ht="15.75" customHeight="1" s="19"/>
-    <row r="190" ht="15.75" customHeight="1" s="19"/>
-    <row r="191" ht="15.75" customHeight="1" s="19"/>
-    <row r="192" ht="15.75" customHeight="1" s="19"/>
-    <row r="193" ht="15.75" customHeight="1" s="19"/>
-    <row r="194" ht="15.75" customHeight="1" s="19"/>
-    <row r="195" ht="15.75" customHeight="1" s="19"/>
-    <row r="196" ht="15.75" customHeight="1" s="19"/>
-    <row r="197" ht="15.75" customHeight="1" s="19"/>
-    <row r="198" ht="15.75" customHeight="1" s="19"/>
-    <row r="199" ht="15.75" customHeight="1" s="19"/>
-    <row r="200" ht="15.75" customHeight="1" s="19"/>
-    <row r="201" ht="15.75" customHeight="1" s="19"/>
-    <row r="202" ht="15.75" customHeight="1" s="19"/>
-    <row r="203" ht="15.75" customHeight="1" s="19"/>
-    <row r="204" ht="15.75" customHeight="1" s="19"/>
-    <row r="205" ht="15.75" customHeight="1" s="19"/>
-    <row r="206" ht="15.75" customHeight="1" s="19"/>
-    <row r="207" ht="15.75" customHeight="1" s="19"/>
-    <row r="208" ht="15.75" customHeight="1" s="19"/>
-    <row r="209" ht="15.75" customHeight="1" s="19"/>
-    <row r="210" ht="15.75" customHeight="1" s="19"/>
-    <row r="211" ht="15.75" customHeight="1" s="19"/>
-    <row r="212" ht="15.75" customHeight="1" s="19"/>
-    <row r="213" ht="15.75" customHeight="1" s="19"/>
-    <row r="214" ht="15.75" customHeight="1" s="19"/>
-    <row r="215" ht="15.75" customHeight="1" s="19"/>
-    <row r="216" ht="15.75" customHeight="1" s="19"/>
-    <row r="217" ht="15.75" customHeight="1" s="19"/>
-    <row r="218" ht="15.75" customHeight="1" s="19"/>
-    <row r="219" ht="15.75" customHeight="1" s="19"/>
-    <row r="220" ht="15.75" customHeight="1" s="19"/>
-    <row r="221" ht="15.75" customHeight="1" s="19"/>
-    <row r="222" ht="15.75" customHeight="1" s="19"/>
-    <row r="223" ht="15.75" customHeight="1" s="19"/>
-    <row r="224" ht="15.75" customHeight="1" s="19"/>
-    <row r="225" ht="15.75" customHeight="1" s="19"/>
-    <row r="226" ht="15.75" customHeight="1" s="19"/>
-    <row r="227" ht="15.75" customHeight="1" s="19"/>
-    <row r="228" ht="15.75" customHeight="1" s="19"/>
-    <row r="229" ht="15.75" customHeight="1" s="19"/>
-    <row r="230" ht="15.75" customHeight="1" s="19"/>
-    <row r="231" ht="15.75" customHeight="1" s="19"/>
-    <row r="232" ht="15.75" customHeight="1" s="19"/>
-    <row r="233" ht="15.75" customHeight="1" s="19"/>
-    <row r="234" ht="15.75" customHeight="1" s="19"/>
-    <row r="235" ht="15.75" customHeight="1" s="19"/>
-    <row r="236" ht="15.75" customHeight="1" s="19"/>
-    <row r="237" ht="15.75" customHeight="1" s="19"/>
-    <row r="238" ht="15.75" customHeight="1" s="19"/>
-    <row r="239" ht="15.75" customHeight="1" s="19"/>
-    <row r="240" ht="15.75" customHeight="1" s="19"/>
-    <row r="241" ht="15.75" customHeight="1" s="19"/>
-    <row r="242" ht="15.75" customHeight="1" s="19"/>
-    <row r="243" ht="15.75" customHeight="1" s="19"/>
-    <row r="244" ht="15.75" customHeight="1" s="19"/>
-    <row r="245" ht="15.75" customHeight="1" s="19"/>
-    <row r="246" ht="15.75" customHeight="1" s="19"/>
-    <row r="247" ht="15.75" customHeight="1" s="19"/>
-    <row r="248" ht="15.75" customHeight="1" s="19"/>
-    <row r="249" ht="15.75" customHeight="1" s="19"/>
-    <row r="250" ht="15.75" customHeight="1" s="19"/>
-    <row r="251" ht="15.75" customHeight="1" s="19"/>
-    <row r="252" ht="15.75" customHeight="1" s="19"/>
-    <row r="253" ht="15.75" customHeight="1" s="19"/>
-    <row r="254" ht="15.75" customHeight="1" s="19"/>
-    <row r="255" ht="15.75" customHeight="1" s="19"/>
-    <row r="256" ht="15.75" customHeight="1" s="19"/>
-    <row r="257" ht="15.75" customHeight="1" s="19"/>
-    <row r="258" ht="15.75" customHeight="1" s="19"/>
-    <row r="259" ht="15.75" customHeight="1" s="19"/>
-    <row r="260" ht="15.75" customHeight="1" s="19"/>
-    <row r="261" ht="15.75" customHeight="1" s="19"/>
-    <row r="262" ht="15.75" customHeight="1" s="19"/>
-    <row r="263" ht="15.75" customHeight="1" s="19"/>
-    <row r="264" ht="15.75" customHeight="1" s="19"/>
-    <row r="265" ht="15.75" customHeight="1" s="19"/>
-    <row r="266" ht="15.75" customHeight="1" s="19"/>
-    <row r="267" ht="15.75" customHeight="1" s="19"/>
-    <row r="268" ht="15.75" customHeight="1" s="19"/>
-    <row r="269" ht="15.75" customHeight="1" s="19"/>
-    <row r="270" ht="15.75" customHeight="1" s="19"/>
-    <row r="271" ht="15.75" customHeight="1" s="19"/>
-    <row r="272" ht="15.75" customHeight="1" s="19"/>
-    <row r="273" ht="15.75" customHeight="1" s="19"/>
-    <row r="274" ht="15.75" customHeight="1" s="19"/>
-    <row r="275" ht="15.75" customHeight="1" s="19"/>
-    <row r="276" ht="15.75" customHeight="1" s="19"/>
-    <row r="277" ht="15.75" customHeight="1" s="19"/>
-    <row r="278" ht="15.75" customHeight="1" s="19"/>
-    <row r="279" ht="15.75" customHeight="1" s="19"/>
-    <row r="280" ht="15.75" customHeight="1" s="19"/>
-    <row r="281" ht="15.75" customHeight="1" s="19"/>
-    <row r="282" ht="15.75" customHeight="1" s="19"/>
-    <row r="283" ht="15.75" customHeight="1" s="19"/>
-    <row r="284" ht="15.75" customHeight="1" s="19"/>
-    <row r="285" ht="15.75" customHeight="1" s="19"/>
-    <row r="286" ht="15.75" customHeight="1" s="19"/>
-    <row r="287" ht="15.75" customHeight="1" s="19"/>
-    <row r="288" ht="15.75" customHeight="1" s="19"/>
-    <row r="289" ht="15.75" customHeight="1" s="19"/>
-    <row r="290" ht="15.75" customHeight="1" s="19"/>
-    <row r="291" ht="15.75" customHeight="1" s="19"/>
-    <row r="292" ht="15.75" customHeight="1" s="19"/>
-    <row r="293" ht="15.75" customHeight="1" s="19"/>
-    <row r="294" ht="15.75" customHeight="1" s="19"/>
-    <row r="295" ht="15.75" customHeight="1" s="19"/>
-    <row r="296" ht="15.75" customHeight="1" s="19"/>
-    <row r="297" ht="15.75" customHeight="1" s="19"/>
-    <row r="298" ht="15.75" customHeight="1" s="19"/>
-    <row r="299" ht="15.75" customHeight="1" s="19"/>
-    <row r="300" ht="15.75" customHeight="1" s="19"/>
-    <row r="301" ht="15.75" customHeight="1" s="19"/>
-    <row r="302" ht="15.75" customHeight="1" s="19"/>
-    <row r="303" ht="15.75" customHeight="1" s="19"/>
-    <row r="304" ht="15.75" customHeight="1" s="19"/>
-    <row r="305" ht="15.75" customHeight="1" s="19"/>
-    <row r="306" ht="15.75" customHeight="1" s="19"/>
-    <row r="307" ht="15.75" customHeight="1" s="19"/>
-    <row r="308" ht="15.75" customHeight="1" s="19"/>
-    <row r="309" ht="15.75" customHeight="1" s="19"/>
-    <row r="310" ht="15.75" customHeight="1" s="19"/>
-    <row r="311" ht="15.75" customHeight="1" s="19"/>
-    <row r="312" ht="15.75" customHeight="1" s="19"/>
-    <row r="313" ht="15.75" customHeight="1" s="19"/>
-    <row r="314" ht="15.75" customHeight="1" s="19"/>
-    <row r="315" ht="15.75" customHeight="1" s="19"/>
-    <row r="316" ht="15.75" customHeight="1" s="19"/>
-    <row r="317" ht="15.75" customHeight="1" s="19"/>
-    <row r="318" ht="15.75" customHeight="1" s="19"/>
-    <row r="319" ht="15.75" customHeight="1" s="19"/>
-    <row r="320" ht="15.75" customHeight="1" s="19"/>
-    <row r="321" ht="15.75" customHeight="1" s="19"/>
-    <row r="322" ht="15.75" customHeight="1" s="19"/>
-    <row r="323" ht="15.75" customHeight="1" s="19"/>
-    <row r="324" ht="15.75" customHeight="1" s="19"/>
-    <row r="325" ht="15.75" customHeight="1" s="19"/>
-    <row r="326" ht="15.75" customHeight="1" s="19"/>
-    <row r="327" ht="15.75" customHeight="1" s="19"/>
-    <row r="328" ht="15.75" customHeight="1" s="19"/>
-    <row r="329" ht="15.75" customHeight="1" s="19"/>
-    <row r="330" ht="15.75" customHeight="1" s="19"/>
-    <row r="331" ht="15.75" customHeight="1" s="19"/>
-    <row r="332" ht="15.75" customHeight="1" s="19"/>
-    <row r="333" ht="15.75" customHeight="1" s="19"/>
-    <row r="334" ht="15.75" customHeight="1" s="19"/>
-    <row r="335" ht="15.75" customHeight="1" s="19"/>
-    <row r="336" ht="15.75" customHeight="1" s="19"/>
-    <row r="337" ht="15.75" customHeight="1" s="19"/>
-    <row r="338" ht="15.75" customHeight="1" s="19"/>
-    <row r="339" ht="15.75" customHeight="1" s="19"/>
-    <row r="340" ht="15.75" customHeight="1" s="19"/>
-    <row r="341" ht="15.75" customHeight="1" s="19"/>
-    <row r="342" ht="15.75" customHeight="1" s="19"/>
-    <row r="343" ht="15.75" customHeight="1" s="19"/>
-    <row r="344" ht="15.75" customHeight="1" s="19"/>
-    <row r="345" ht="15.75" customHeight="1" s="19"/>
-    <row r="346" ht="15.75" customHeight="1" s="19"/>
-    <row r="347" ht="15.75" customHeight="1" s="19"/>
-    <row r="348" ht="15.75" customHeight="1" s="19"/>
-    <row r="349" ht="15.75" customHeight="1" s="19"/>
-    <row r="350" ht="15.75" customHeight="1" s="19"/>
-    <row r="351" ht="15.75" customHeight="1" s="19"/>
-    <row r="352" ht="15.75" customHeight="1" s="19"/>
-    <row r="353" ht="15.75" customHeight="1" s="19"/>
-    <row r="354" ht="15.75" customHeight="1" s="19"/>
-    <row r="355" ht="15.75" customHeight="1" s="19"/>
-    <row r="356" ht="15.75" customHeight="1" s="19"/>
-    <row r="357" ht="15.75" customHeight="1" s="19"/>
-    <row r="358" ht="15.75" customHeight="1" s="19"/>
-    <row r="359" ht="15.75" customHeight="1" s="19"/>
-    <row r="360" ht="15.75" customHeight="1" s="19"/>
-    <row r="361" ht="15.75" customHeight="1" s="19"/>
-    <row r="362" ht="15.75" customHeight="1" s="19"/>
-    <row r="363" ht="15.75" customHeight="1" s="19"/>
-    <row r="364" ht="15.75" customHeight="1" s="19"/>
-    <row r="365" ht="15.75" customHeight="1" s="19"/>
-    <row r="366" ht="15.75" customHeight="1" s="19"/>
-    <row r="367" ht="15.75" customHeight="1" s="19"/>
-    <row r="368" ht="15.75" customHeight="1" s="19"/>
-    <row r="369" ht="15.75" customHeight="1" s="19"/>
-    <row r="370" ht="15.75" customHeight="1" s="19"/>
-    <row r="371" ht="15.75" customHeight="1" s="19"/>
-    <row r="372" ht="15.75" customHeight="1" s="19"/>
-    <row r="373" ht="15.75" customHeight="1" s="19"/>
-    <row r="374" ht="15.75" customHeight="1" s="19"/>
-    <row r="375" ht="15.75" customHeight="1" s="19"/>
-    <row r="376" ht="15.75" customHeight="1" s="19"/>
-    <row r="377" ht="15.75" customHeight="1" s="19"/>
-    <row r="378" ht="15.75" customHeight="1" s="19"/>
-    <row r="379" ht="15.75" customHeight="1" s="19"/>
-    <row r="380" ht="15.75" customHeight="1" s="19"/>
-    <row r="381" ht="15.75" customHeight="1" s="19"/>
-    <row r="382" ht="15.75" customHeight="1" s="19"/>
-    <row r="383" ht="15.75" customHeight="1" s="19"/>
-    <row r="384" ht="15.75" customHeight="1" s="19"/>
-    <row r="385" ht="15.75" customHeight="1" s="19"/>
-    <row r="386" ht="15.75" customHeight="1" s="19"/>
-    <row r="387" ht="15.75" customHeight="1" s="19"/>
-    <row r="388" ht="15.75" customHeight="1" s="19"/>
-    <row r="389" ht="15.75" customHeight="1" s="19"/>
-    <row r="390" ht="15.75" customHeight="1" s="19"/>
-    <row r="391" ht="15.75" customHeight="1" s="19"/>
-    <row r="392" ht="15.75" customHeight="1" s="19"/>
-    <row r="393" ht="15.75" customHeight="1" s="19"/>
-    <row r="394" ht="15.75" customHeight="1" s="19"/>
-    <row r="395" ht="15.75" customHeight="1" s="19"/>
-    <row r="396" ht="15.75" customHeight="1" s="19"/>
-    <row r="397" ht="15.75" customHeight="1" s="19"/>
-    <row r="398" ht="15.75" customHeight="1" s="19"/>
-    <row r="399" ht="15.75" customHeight="1" s="19"/>
-    <row r="400" ht="15.75" customHeight="1" s="19"/>
-    <row r="401" ht="15.75" customHeight="1" s="19"/>
-    <row r="402" ht="15.75" customHeight="1" s="19"/>
-    <row r="403" ht="15.75" customHeight="1" s="19"/>
-    <row r="404" ht="15.75" customHeight="1" s="19"/>
-    <row r="405" ht="15.75" customHeight="1" s="19"/>
-    <row r="406" ht="15.75" customHeight="1" s="19"/>
-    <row r="407" ht="15.75" customHeight="1" s="19"/>
-    <row r="408" ht="15.75" customHeight="1" s="19"/>
-    <row r="409" ht="15.75" customHeight="1" s="19"/>
-    <row r="410" ht="15.75" customHeight="1" s="19"/>
-    <row r="411" ht="15.75" customHeight="1" s="19"/>
-    <row r="412" ht="15.75" customHeight="1" s="19"/>
-    <row r="413" ht="15.75" customHeight="1" s="19"/>
-    <row r="414" ht="15.75" customHeight="1" s="19"/>
-    <row r="415" ht="15.75" customHeight="1" s="19"/>
-    <row r="416" ht="15.75" customHeight="1" s="19"/>
-    <row r="417" ht="15.75" customHeight="1" s="19"/>
-    <row r="418" ht="15.75" customHeight="1" s="19"/>
-    <row r="419" ht="15.75" customHeight="1" s="19"/>
-    <row r="420" ht="15.75" customHeight="1" s="19"/>
-    <row r="421" ht="15.75" customHeight="1" s="19"/>
-    <row r="422" ht="15.75" customHeight="1" s="19"/>
-    <row r="423" ht="15.75" customHeight="1" s="19"/>
-    <row r="424" ht="15.75" customHeight="1" s="19"/>
-    <row r="425" ht="15.75" customHeight="1" s="19"/>
-    <row r="426" ht="15.75" customHeight="1" s="19"/>
-    <row r="427" ht="15.75" customHeight="1" s="19"/>
-    <row r="428" ht="15.75" customHeight="1" s="19"/>
-    <row r="429" ht="15.75" customHeight="1" s="19"/>
-    <row r="430" ht="15.75" customHeight="1" s="19"/>
-    <row r="431" ht="15.75" customHeight="1" s="19"/>
-    <row r="432" ht="15.75" customHeight="1" s="19"/>
-    <row r="433" ht="15.75" customHeight="1" s="19"/>
-    <row r="434" ht="15.75" customHeight="1" s="19"/>
-    <row r="435" ht="15.75" customHeight="1" s="19"/>
-    <row r="436" ht="15.75" customHeight="1" s="19"/>
-    <row r="437" ht="15.75" customHeight="1" s="19"/>
-    <row r="438" ht="15.75" customHeight="1" s="19"/>
-    <row r="439" ht="15.75" customHeight="1" s="19"/>
-    <row r="440" ht="15.75" customHeight="1" s="19"/>
-    <row r="441" ht="15.75" customHeight="1" s="19"/>
-    <row r="442" ht="15.75" customHeight="1" s="19"/>
-    <row r="443" ht="15.75" customHeight="1" s="19"/>
-    <row r="444" ht="15.75" customHeight="1" s="19"/>
-    <row r="445" ht="15.75" customHeight="1" s="19"/>
-    <row r="446" ht="15.75" customHeight="1" s="19"/>
-    <row r="447" ht="15.75" customHeight="1" s="19"/>
-    <row r="448" ht="15.75" customHeight="1" s="19"/>
-    <row r="449" ht="15.75" customHeight="1" s="19"/>
-    <row r="450" ht="15.75" customHeight="1" s="19"/>
-    <row r="451" ht="15.75" customHeight="1" s="19"/>
-    <row r="452" ht="15.75" customHeight="1" s="19"/>
-    <row r="453" ht="15.75" customHeight="1" s="19"/>
-    <row r="454" ht="15.75" customHeight="1" s="19"/>
-    <row r="455" ht="15.75" customHeight="1" s="19"/>
-    <row r="456" ht="15.75" customHeight="1" s="19"/>
-    <row r="457" ht="15.75" customHeight="1" s="19"/>
-    <row r="458" ht="15.75" customHeight="1" s="19"/>
-    <row r="459" ht="15.75" customHeight="1" s="19"/>
-    <row r="460" ht="15.75" customHeight="1" s="19"/>
-    <row r="461" ht="15.75" customHeight="1" s="19"/>
-    <row r="462" ht="15.75" customHeight="1" s="19"/>
-    <row r="463" ht="15.75" customHeight="1" s="19"/>
-    <row r="464" ht="15.75" customHeight="1" s="19"/>
-    <row r="465" ht="15.75" customHeight="1" s="19"/>
-    <row r="466" ht="15.75" customHeight="1" s="19"/>
-    <row r="467" ht="15.75" customHeight="1" s="19"/>
-    <row r="468" ht="15.75" customHeight="1" s="19"/>
-    <row r="469" ht="15.75" customHeight="1" s="19"/>
-    <row r="470" ht="15.75" customHeight="1" s="19"/>
-    <row r="471" ht="15.75" customHeight="1" s="19"/>
-    <row r="472" ht="15.75" customHeight="1" s="19"/>
-    <row r="473" ht="15.75" customHeight="1" s="19"/>
-    <row r="474" ht="15.75" customHeight="1" s="19"/>
-    <row r="475" ht="15.75" customHeight="1" s="19"/>
-    <row r="476" ht="15.75" customHeight="1" s="19"/>
-    <row r="477" ht="15.75" customHeight="1" s="19"/>
-    <row r="478" ht="15.75" customHeight="1" s="19"/>
-    <row r="479" ht="15.75" customHeight="1" s="19"/>
-    <row r="480" ht="15.75" customHeight="1" s="19"/>
-    <row r="481" ht="15.75" customHeight="1" s="19"/>
-    <row r="482" ht="15.75" customHeight="1" s="19"/>
-    <row r="483" ht="15.75" customHeight="1" s="19"/>
-    <row r="484" ht="15.75" customHeight="1" s="19"/>
-    <row r="485" ht="15.75" customHeight="1" s="19"/>
-    <row r="486" ht="15.75" customHeight="1" s="19"/>
-    <row r="487" ht="15.75" customHeight="1" s="19"/>
-    <row r="488" ht="15.75" customHeight="1" s="19"/>
-    <row r="489" ht="15.75" customHeight="1" s="19"/>
-    <row r="490" ht="15.75" customHeight="1" s="19"/>
-    <row r="491" ht="15.75" customHeight="1" s="19"/>
-    <row r="492" ht="15.75" customHeight="1" s="19"/>
-    <row r="493" ht="15.75" customHeight="1" s="19"/>
-    <row r="494" ht="15.75" customHeight="1" s="19"/>
-    <row r="495" ht="15.75" customHeight="1" s="19"/>
-    <row r="496" ht="15.75" customHeight="1" s="19"/>
-    <row r="497" ht="15.75" customHeight="1" s="19"/>
-    <row r="498" ht="15.75" customHeight="1" s="19"/>
-    <row r="499" ht="15.75" customHeight="1" s="19"/>
-    <row r="500" ht="15.75" customHeight="1" s="19"/>
-    <row r="501" ht="15.75" customHeight="1" s="19"/>
-    <row r="502" ht="15.75" customHeight="1" s="19"/>
-    <row r="503" ht="15.75" customHeight="1" s="19"/>
-    <row r="504" ht="15.75" customHeight="1" s="19"/>
-    <row r="505" ht="15.75" customHeight="1" s="19"/>
-    <row r="506" ht="15.75" customHeight="1" s="19"/>
-    <row r="507" ht="15.75" customHeight="1" s="19"/>
-    <row r="508" ht="15.75" customHeight="1" s="19"/>
-    <row r="509" ht="15.75" customHeight="1" s="19"/>
-    <row r="510" ht="15.75" customHeight="1" s="19"/>
-    <row r="511" ht="15.75" customHeight="1" s="19"/>
-    <row r="512" ht="15.75" customHeight="1" s="19"/>
-    <row r="513" ht="15.75" customHeight="1" s="19"/>
-    <row r="514" ht="15.75" customHeight="1" s="19"/>
-    <row r="515" ht="15.75" customHeight="1" s="19"/>
-    <row r="516" ht="15.75" customHeight="1" s="19"/>
-    <row r="517" ht="15.75" customHeight="1" s="19"/>
-    <row r="518" ht="15.75" customHeight="1" s="19"/>
-    <row r="519" ht="15.75" customHeight="1" s="19"/>
-    <row r="520" ht="15.75" customHeight="1" s="19"/>
-    <row r="521" ht="15.75" customHeight="1" s="19"/>
-    <row r="522" ht="15.75" customHeight="1" s="19"/>
-    <row r="523" ht="15.75" customHeight="1" s="19"/>
-    <row r="524" ht="15.75" customHeight="1" s="19"/>
-    <row r="525" ht="15.75" customHeight="1" s="19"/>
-    <row r="526" ht="15.75" customHeight="1" s="19"/>
-    <row r="527" ht="15.75" customHeight="1" s="19"/>
-    <row r="528" ht="15.75" customHeight="1" s="19"/>
-    <row r="529" ht="15.75" customHeight="1" s="19"/>
-    <row r="530" ht="15.75" customHeight="1" s="19"/>
-    <row r="531" ht="15.75" customHeight="1" s="19"/>
-    <row r="532" ht="15.75" customHeight="1" s="19"/>
-    <row r="533" ht="15.75" customHeight="1" s="19"/>
-    <row r="534" ht="15.75" customHeight="1" s="19"/>
-    <row r="535" ht="15.75" customHeight="1" s="19"/>
-    <row r="536" ht="15.75" customHeight="1" s="19"/>
-    <row r="537" ht="15.75" customHeight="1" s="19"/>
-    <row r="538" ht="15.75" customHeight="1" s="19"/>
-    <row r="539" ht="15.75" customHeight="1" s="19"/>
-    <row r="540" ht="15.75" customHeight="1" s="19"/>
-    <row r="541" ht="15.75" customHeight="1" s="19"/>
-    <row r="542" ht="15.75" customHeight="1" s="19"/>
-    <row r="543" ht="15.75" customHeight="1" s="19"/>
-    <row r="544" ht="15.75" customHeight="1" s="19"/>
-    <row r="545" ht="15.75" customHeight="1" s="19"/>
-    <row r="546" ht="15.75" customHeight="1" s="19"/>
-    <row r="547" ht="15.75" customHeight="1" s="19"/>
-    <row r="548" ht="15.75" customHeight="1" s="19"/>
-    <row r="549" ht="15.75" customHeight="1" s="19"/>
-    <row r="550" ht="15.75" customHeight="1" s="19"/>
-    <row r="551" ht="15.75" customHeight="1" s="19"/>
-    <row r="552" ht="15.75" customHeight="1" s="19"/>
-    <row r="553" ht="15.75" customHeight="1" s="19"/>
-    <row r="554" ht="15.75" customHeight="1" s="19"/>
-    <row r="555" ht="15.75" customHeight="1" s="19"/>
-    <row r="556" ht="15.75" customHeight="1" s="19"/>
-    <row r="557" ht="15.75" customHeight="1" s="19"/>
-    <row r="558" ht="15.75" customHeight="1" s="19"/>
-    <row r="559" ht="15.75" customHeight="1" s="19"/>
-    <row r="560" ht="15.75" customHeight="1" s="19"/>
-    <row r="561" ht="15.75" customHeight="1" s="19"/>
-    <row r="562" ht="15.75" customHeight="1" s="19"/>
-    <row r="563" ht="15.75" customHeight="1" s="19"/>
-    <row r="564" ht="15.75" customHeight="1" s="19"/>
-    <row r="565" ht="15.75" customHeight="1" s="19"/>
-    <row r="566" ht="15.75" customHeight="1" s="19"/>
-    <row r="567" ht="15.75" customHeight="1" s="19"/>
-    <row r="568" ht="15.75" customHeight="1" s="19"/>
-    <row r="569" ht="15.75" customHeight="1" s="19"/>
-    <row r="570" ht="15.75" customHeight="1" s="19"/>
-    <row r="571" ht="15.75" customHeight="1" s="19"/>
-    <row r="572" ht="15.75" customHeight="1" s="19"/>
-    <row r="573" ht="15.75" customHeight="1" s="19"/>
-    <row r="574" ht="15.75" customHeight="1" s="19"/>
-    <row r="575" ht="15.75" customHeight="1" s="19"/>
-    <row r="576" ht="15.75" customHeight="1" s="19"/>
-    <row r="577" ht="15.75" customHeight="1" s="19"/>
-    <row r="578" ht="15.75" customHeight="1" s="19"/>
-    <row r="579" ht="15.75" customHeight="1" s="19"/>
-    <row r="580" ht="15.75" customHeight="1" s="19"/>
-    <row r="581" ht="15.75" customHeight="1" s="19"/>
-    <row r="582" ht="15.75" customHeight="1" s="19"/>
-    <row r="583" ht="15.75" customHeight="1" s="19"/>
-    <row r="584" ht="15.75" customHeight="1" s="19"/>
-    <row r="585" ht="15.75" customHeight="1" s="19"/>
-    <row r="586" ht="15.75" customHeight="1" s="19"/>
-    <row r="587" ht="15.75" customHeight="1" s="19"/>
-    <row r="588" ht="15.75" customHeight="1" s="19"/>
-    <row r="589" ht="15.75" customHeight="1" s="19"/>
-    <row r="590" ht="15.75" customHeight="1" s="19"/>
-    <row r="591" ht="15.75" customHeight="1" s="19"/>
-    <row r="592" ht="15.75" customHeight="1" s="19"/>
-    <row r="593" ht="15.75" customHeight="1" s="19"/>
-    <row r="594" ht="15.75" customHeight="1" s="19"/>
-    <row r="595" ht="15.75" customHeight="1" s="19"/>
-    <row r="596" ht="15.75" customHeight="1" s="19"/>
-    <row r="597" ht="15.75" customHeight="1" s="19"/>
-    <row r="598" ht="15.75" customHeight="1" s="19"/>
-    <row r="599" ht="15.75" customHeight="1" s="19"/>
-    <row r="600" ht="15.75" customHeight="1" s="19"/>
-    <row r="601" ht="15.75" customHeight="1" s="19"/>
-    <row r="602" ht="15.75" customHeight="1" s="19"/>
-    <row r="603" ht="15.75" customHeight="1" s="19"/>
-    <row r="604" ht="15.75" customHeight="1" s="19"/>
-    <row r="605" ht="15.75" customHeight="1" s="19"/>
-    <row r="606" ht="15.75" customHeight="1" s="19"/>
-    <row r="607" ht="15.75" customHeight="1" s="19"/>
-    <row r="608" ht="15.75" customHeight="1" s="19"/>
-    <row r="609" ht="15.75" customHeight="1" s="19"/>
-    <row r="610" ht="15.75" customHeight="1" s="19"/>
-    <row r="611" ht="15.75" customHeight="1" s="19"/>
-    <row r="612" ht="15.75" customHeight="1" s="19"/>
-    <row r="613" ht="15.75" customHeight="1" s="19"/>
-    <row r="614" ht="15.75" customHeight="1" s="19"/>
-    <row r="615" ht="15.75" customHeight="1" s="19"/>
-    <row r="616" ht="15.75" customHeight="1" s="19"/>
-    <row r="617" ht="15.75" customHeight="1" s="19"/>
-    <row r="618" ht="15.75" customHeight="1" s="19"/>
-    <row r="619" ht="15.75" customHeight="1" s="19"/>
-    <row r="620" ht="15.75" customHeight="1" s="19"/>
-    <row r="621" ht="15.75" customHeight="1" s="19"/>
-    <row r="622" ht="15.75" customHeight="1" s="19"/>
-    <row r="623" ht="15.75" customHeight="1" s="19"/>
-    <row r="624" ht="15.75" customHeight="1" s="19"/>
-    <row r="625" ht="15.75" customHeight="1" s="19"/>
-    <row r="626" ht="15.75" customHeight="1" s="19"/>
-    <row r="627" ht="15.75" customHeight="1" s="19"/>
-    <row r="628" ht="15.75" customHeight="1" s="19"/>
-    <row r="629" ht="15.75" customHeight="1" s="19"/>
-    <row r="630" ht="15.75" customHeight="1" s="19"/>
-    <row r="631" ht="15.75" customHeight="1" s="19"/>
-    <row r="632" ht="15.75" customHeight="1" s="19"/>
-    <row r="633" ht="15.75" customHeight="1" s="19"/>
-    <row r="634" ht="15.75" customHeight="1" s="19"/>
-    <row r="635" ht="15.75" customHeight="1" s="19"/>
-    <row r="636" ht="15.75" customHeight="1" s="19"/>
-    <row r="637" ht="15.75" customHeight="1" s="19"/>
-    <row r="638" ht="15.75" customHeight="1" s="19"/>
-    <row r="639" ht="15.75" customHeight="1" s="19"/>
-    <row r="640" ht="15.75" customHeight="1" s="19"/>
-    <row r="641" ht="15.75" customHeight="1" s="19"/>
-    <row r="642" ht="15.75" customHeight="1" s="19"/>
-    <row r="643" ht="15.75" customHeight="1" s="19"/>
-    <row r="644" ht="15.75" customHeight="1" s="19"/>
-    <row r="645" ht="15.75" customHeight="1" s="19"/>
-    <row r="646" ht="15.75" customHeight="1" s="19"/>
-    <row r="647" ht="15.75" customHeight="1" s="19"/>
-    <row r="648" ht="15.75" customHeight="1" s="19"/>
-    <row r="649" ht="15.75" customHeight="1" s="19"/>
-    <row r="650" ht="15.75" customHeight="1" s="19"/>
-    <row r="651" ht="15.75" customHeight="1" s="19"/>
-    <row r="652" ht="15.75" customHeight="1" s="19"/>
-    <row r="653" ht="15.75" customHeight="1" s="19"/>
-    <row r="654" ht="15.75" customHeight="1" s="19"/>
-    <row r="655" ht="15.75" customHeight="1" s="19"/>
-    <row r="656" ht="15.75" customHeight="1" s="19"/>
-    <row r="657" ht="15.75" customHeight="1" s="19"/>
-    <row r="658" ht="15.75" customHeight="1" s="19"/>
-    <row r="659" ht="15.75" customHeight="1" s="19"/>
-    <row r="660" ht="15.75" customHeight="1" s="19"/>
-    <row r="661" ht="15.75" customHeight="1" s="19"/>
-    <row r="662" ht="15.75" customHeight="1" s="19"/>
-    <row r="663" ht="15.75" customHeight="1" s="19"/>
-    <row r="664" ht="15.75" customHeight="1" s="19"/>
-    <row r="665" ht="15.75" customHeight="1" s="19"/>
-    <row r="666" ht="15.75" customHeight="1" s="19"/>
-    <row r="667" ht="15.75" customHeight="1" s="19"/>
-    <row r="668" ht="15.75" customHeight="1" s="19"/>
-    <row r="669" ht="15.75" customHeight="1" s="19"/>
-    <row r="670" ht="15.75" customHeight="1" s="19"/>
-    <row r="671" ht="15.75" customHeight="1" s="19"/>
-    <row r="672" ht="15.75" customHeight="1" s="19"/>
-    <row r="673" ht="15.75" customHeight="1" s="19"/>
-    <row r="674" ht="15.75" customHeight="1" s="19"/>
-    <row r="675" ht="15.75" customHeight="1" s="19"/>
-    <row r="676" ht="15.75" customHeight="1" s="19"/>
-    <row r="677" ht="15.75" customHeight="1" s="19"/>
-    <row r="678" ht="15.75" customHeight="1" s="19"/>
-    <row r="679" ht="15.75" customHeight="1" s="19"/>
-    <row r="680" ht="15.75" customHeight="1" s="19"/>
-    <row r="681" ht="15.75" customHeight="1" s="19"/>
-    <row r="682" ht="15.75" customHeight="1" s="19"/>
-    <row r="683" ht="15.75" customHeight="1" s="19"/>
-    <row r="684" ht="15.75" customHeight="1" s="19"/>
-    <row r="685" ht="15.75" customHeight="1" s="19"/>
-    <row r="686" ht="15.75" customHeight="1" s="19"/>
-    <row r="687" ht="15.75" customHeight="1" s="19"/>
-    <row r="688" ht="15.75" customHeight="1" s="19"/>
-    <row r="689" ht="15.75" customHeight="1" s="19"/>
-    <row r="690" ht="15.75" customHeight="1" s="19"/>
-    <row r="691" ht="15.75" customHeight="1" s="19"/>
-    <row r="692" ht="15.75" customHeight="1" s="19"/>
-    <row r="693" ht="15.75" customHeight="1" s="19"/>
-    <row r="694" ht="15.75" customHeight="1" s="19"/>
-    <row r="695" ht="15.75" customHeight="1" s="19"/>
-    <row r="696" ht="15.75" customHeight="1" s="19"/>
-    <row r="697" ht="15.75" customHeight="1" s="19"/>
-    <row r="698" ht="15.75" customHeight="1" s="19"/>
-    <row r="699" ht="15.75" customHeight="1" s="19"/>
-    <row r="700" ht="15.75" customHeight="1" s="19"/>
-    <row r="701" ht="15.75" customHeight="1" s="19"/>
-    <row r="702" ht="15.75" customHeight="1" s="19"/>
-    <row r="703" ht="15.75" customHeight="1" s="19"/>
-    <row r="704" ht="15.75" customHeight="1" s="19"/>
-    <row r="705" ht="15.75" customHeight="1" s="19"/>
-    <row r="706" ht="15.75" customHeight="1" s="19"/>
-    <row r="707" ht="15.75" customHeight="1" s="19"/>
-    <row r="708" ht="15.75" customHeight="1" s="19"/>
-    <row r="709" ht="15.75" customHeight="1" s="19"/>
-    <row r="710" ht="15.75" customHeight="1" s="19"/>
-    <row r="711" ht="15.75" customHeight="1" s="19"/>
-    <row r="712" ht="15.75" customHeight="1" s="19"/>
-    <row r="713" ht="15.75" customHeight="1" s="19"/>
-    <row r="714" ht="15.75" customHeight="1" s="19"/>
-    <row r="715" ht="15.75" customHeight="1" s="19"/>
-    <row r="716" ht="15.75" customHeight="1" s="19"/>
-    <row r="717" ht="15.75" customHeight="1" s="19"/>
-    <row r="718" ht="15.75" customHeight="1" s="19"/>
-    <row r="719" ht="15.75" customHeight="1" s="19"/>
-    <row r="720" ht="15.75" customHeight="1" s="19"/>
-    <row r="721" ht="15.75" customHeight="1" s="19"/>
-    <row r="722" ht="15.75" customHeight="1" s="19"/>
-    <row r="723" ht="15.75" customHeight="1" s="19"/>
-    <row r="724" ht="15.75" customHeight="1" s="19"/>
-    <row r="725" ht="15.75" customHeight="1" s="19"/>
-    <row r="726" ht="15.75" customHeight="1" s="19"/>
-    <row r="727" ht="15.75" customHeight="1" s="19"/>
-    <row r="728" ht="15.75" customHeight="1" s="19"/>
-    <row r="729" ht="15.75" customHeight="1" s="19"/>
-    <row r="730" ht="15.75" customHeight="1" s="19"/>
-    <row r="731" ht="15.75" customHeight="1" s="19"/>
-    <row r="732" ht="15.75" customHeight="1" s="19"/>
-    <row r="733" ht="15.75" customHeight="1" s="19"/>
-    <row r="734" ht="15.75" customHeight="1" s="19"/>
-    <row r="735" ht="15.75" customHeight="1" s="19"/>
-    <row r="736" ht="15.75" customHeight="1" s="19"/>
-    <row r="737" ht="15.75" customHeight="1" s="19"/>
-    <row r="738" ht="15.75" customHeight="1" s="19"/>
-    <row r="739" ht="15.75" customHeight="1" s="19"/>
-    <row r="740" ht="15.75" customHeight="1" s="19"/>
-    <row r="741" ht="15.75" customHeight="1" s="19"/>
-    <row r="742" ht="15.75" customHeight="1" s="19"/>
-    <row r="743" ht="15.75" customHeight="1" s="19"/>
-    <row r="744" ht="15.75" customHeight="1" s="19"/>
-    <row r="745" ht="15.75" customHeight="1" s="19"/>
-    <row r="746" ht="15.75" customHeight="1" s="19"/>
-    <row r="747" ht="15.75" customHeight="1" s="19"/>
-    <row r="748" ht="15.75" customHeight="1" s="19"/>
-    <row r="749" ht="15.75" customHeight="1" s="19"/>
-    <row r="750" ht="15.75" customHeight="1" s="19"/>
-    <row r="751" ht="15.75" customHeight="1" s="19"/>
-    <row r="752" ht="15.75" customHeight="1" s="19"/>
-    <row r="753" ht="15.75" customHeight="1" s="19"/>
-    <row r="754" ht="15.75" customHeight="1" s="19"/>
-    <row r="755" ht="15.75" customHeight="1" s="19"/>
-    <row r="756" ht="15.75" customHeight="1" s="19"/>
-    <row r="757" ht="15.75" customHeight="1" s="19"/>
-    <row r="758" ht="15.75" customHeight="1" s="19"/>
-    <row r="759" ht="15.75" customHeight="1" s="19"/>
-    <row r="760" ht="15.75" customHeight="1" s="19"/>
-    <row r="761" ht="15.75" customHeight="1" s="19"/>
-    <row r="762" ht="15.75" customHeight="1" s="19"/>
-    <row r="763" ht="15.75" customHeight="1" s="19"/>
-    <row r="764" ht="15.75" customHeight="1" s="19"/>
-    <row r="765" ht="15.75" customHeight="1" s="19"/>
-    <row r="766" ht="15.75" customHeight="1" s="19"/>
-    <row r="767" ht="15.75" customHeight="1" s="19"/>
-    <row r="768" ht="15.75" customHeight="1" s="19"/>
-    <row r="769" ht="15.75" customHeight="1" s="19"/>
-    <row r="770" ht="15.75" customHeight="1" s="19"/>
-    <row r="771" ht="15.75" customHeight="1" s="19"/>
-    <row r="772" ht="15.75" customHeight="1" s="19"/>
-    <row r="773" ht="15.75" customHeight="1" s="19"/>
-    <row r="774" ht="15.75" customHeight="1" s="19"/>
-    <row r="775" ht="15.75" customHeight="1" s="19"/>
-    <row r="776" ht="15.75" customHeight="1" s="19"/>
-    <row r="777" ht="15.75" customHeight="1" s="19"/>
-    <row r="778" ht="15.75" customHeight="1" s="19"/>
-    <row r="779" ht="15.75" customHeight="1" s="19"/>
-    <row r="780" ht="15.75" customHeight="1" s="19"/>
-    <row r="781" ht="15.75" customHeight="1" s="19"/>
-    <row r="782" ht="15.75" customHeight="1" s="19"/>
-    <row r="783" ht="15.75" customHeight="1" s="19"/>
-    <row r="784" ht="15.75" customHeight="1" s="19"/>
-    <row r="785" ht="15.75" customHeight="1" s="19"/>
-    <row r="786" ht="15.75" customHeight="1" s="19"/>
-    <row r="787" ht="15.75" customHeight="1" s="19"/>
-    <row r="788" ht="15.75" customHeight="1" s="19"/>
-    <row r="789" ht="15.75" customHeight="1" s="19"/>
-    <row r="790" ht="15.75" customHeight="1" s="19"/>
-    <row r="791" ht="15.75" customHeight="1" s="19"/>
-    <row r="792" ht="15.75" customHeight="1" s="19"/>
-    <row r="793" ht="15.75" customHeight="1" s="19"/>
-    <row r="794" ht="15.75" customHeight="1" s="19"/>
-    <row r="795" ht="15.75" customHeight="1" s="19"/>
-    <row r="796" ht="15.75" customHeight="1" s="19"/>
-    <row r="797" ht="15.75" customHeight="1" s="19"/>
-    <row r="798" ht="15.75" customHeight="1" s="19"/>
-    <row r="799" ht="15.75" customHeight="1" s="19"/>
-    <row r="800" ht="15.75" customHeight="1" s="19"/>
-    <row r="801" ht="15.75" customHeight="1" s="19"/>
-    <row r="802" ht="15.75" customHeight="1" s="19"/>
-    <row r="803" ht="15.75" customHeight="1" s="19"/>
-    <row r="804" ht="15.75" customHeight="1" s="19"/>
-    <row r="805" ht="15.75" customHeight="1" s="19"/>
-    <row r="806" ht="15.75" customHeight="1" s="19"/>
-    <row r="807" ht="15.75" customHeight="1" s="19"/>
-    <row r="808" ht="15.75" customHeight="1" s="19"/>
-    <row r="809" ht="15.75" customHeight="1" s="19"/>
-    <row r="810" ht="15.75" customHeight="1" s="19"/>
-    <row r="811" ht="15.75" customHeight="1" s="19"/>
-    <row r="812" ht="15.75" customHeight="1" s="19"/>
-    <row r="813" ht="15.75" customHeight="1" s="19"/>
-    <row r="814" ht="15.75" customHeight="1" s="19"/>
-    <row r="815" ht="15.75" customHeight="1" s="19"/>
-    <row r="816" ht="15.75" customHeight="1" s="19"/>
-    <row r="817" ht="15.75" customHeight="1" s="19"/>
-    <row r="818" ht="15.75" customHeight="1" s="19"/>
-    <row r="819" ht="15.75" customHeight="1" s="19"/>
-    <row r="820" ht="15.75" customHeight="1" s="19"/>
-    <row r="821" ht="15.75" customHeight="1" s="19"/>
-    <row r="822" ht="15.75" customHeight="1" s="19"/>
-    <row r="823" ht="15.75" customHeight="1" s="19"/>
-    <row r="824" ht="15.75" customHeight="1" s="19"/>
-    <row r="825" ht="15.75" customHeight="1" s="19"/>
-    <row r="826" ht="15.75" customHeight="1" s="19"/>
-    <row r="827" ht="15.75" customHeight="1" s="19"/>
-    <row r="828" ht="15.75" customHeight="1" s="19"/>
-    <row r="829" ht="15.75" customHeight="1" s="19"/>
-    <row r="830" ht="15.75" customHeight="1" s="19"/>
-    <row r="831" ht="15.75" customHeight="1" s="19"/>
-    <row r="832" ht="15.75" customHeight="1" s="19"/>
-    <row r="833" ht="15.75" customHeight="1" s="19"/>
-    <row r="834" ht="15.75" customHeight="1" s="19"/>
-    <row r="835" ht="15.75" customHeight="1" s="19"/>
-    <row r="836" ht="15.75" customHeight="1" s="19"/>
-    <row r="837" ht="15.75" customHeight="1" s="19"/>
-    <row r="838" ht="15.75" customHeight="1" s="19"/>
-    <row r="839" ht="15.75" customHeight="1" s="19"/>
-    <row r="840" ht="15.75" customHeight="1" s="19"/>
-    <row r="841" ht="15.75" customHeight="1" s="19"/>
-    <row r="842" ht="15.75" customHeight="1" s="19"/>
-    <row r="843" ht="15.75" customHeight="1" s="19"/>
-    <row r="844" ht="15.75" customHeight="1" s="19"/>
-    <row r="845" ht="15.75" customHeight="1" s="19"/>
-    <row r="846" ht="15.75" customHeight="1" s="19"/>
-    <row r="847" ht="15.75" customHeight="1" s="19"/>
-    <row r="848" ht="15.75" customHeight="1" s="19"/>
-    <row r="849" ht="15.75" customHeight="1" s="19"/>
-    <row r="850" ht="15.75" customHeight="1" s="19"/>
-    <row r="851" ht="15.75" customHeight="1" s="19"/>
-    <row r="852" ht="15.75" customHeight="1" s="19"/>
-    <row r="853" ht="15.75" customHeight="1" s="19"/>
-    <row r="854" ht="15.75" customHeight="1" s="19"/>
-    <row r="855" ht="15.75" customHeight="1" s="19"/>
-    <row r="856" ht="15.75" customHeight="1" s="19"/>
-    <row r="857" ht="15.75" customHeight="1" s="19"/>
-    <row r="858" ht="15.75" customHeight="1" s="19"/>
-    <row r="859" ht="15.75" customHeight="1" s="19"/>
-    <row r="860" ht="15.75" customHeight="1" s="19"/>
-    <row r="861" ht="15.75" customHeight="1" s="19"/>
-    <row r="862" ht="15.75" customHeight="1" s="19"/>
-    <row r="863" ht="15.75" customHeight="1" s="19"/>
-    <row r="864" ht="15.75" customHeight="1" s="19"/>
-    <row r="865" ht="15.75" customHeight="1" s="19"/>
-    <row r="866" ht="15.75" customHeight="1" s="19"/>
-    <row r="867" ht="15.75" customHeight="1" s="19"/>
-    <row r="868" ht="15.75" customHeight="1" s="19"/>
-    <row r="869" ht="15.75" customHeight="1" s="19"/>
-    <row r="870" ht="15.75" customHeight="1" s="19"/>
-    <row r="871" ht="15.75" customHeight="1" s="19"/>
-    <row r="872" ht="15.75" customHeight="1" s="19"/>
-    <row r="873" ht="15.75" customHeight="1" s="19"/>
-    <row r="874" ht="15.75" customHeight="1" s="19"/>
-    <row r="875" ht="15.75" customHeight="1" s="19"/>
-    <row r="876" ht="15.75" customHeight="1" s="19"/>
-    <row r="877" ht="15.75" customHeight="1" s="19"/>
-    <row r="878" ht="15.75" customHeight="1" s="19"/>
-    <row r="879" ht="15.75" customHeight="1" s="19"/>
-    <row r="880" ht="15.75" customHeight="1" s="19"/>
-    <row r="881" ht="15.75" customHeight="1" s="19"/>
-    <row r="882" ht="15.75" customHeight="1" s="19"/>
-    <row r="883" ht="15.75" customHeight="1" s="19"/>
-    <row r="884" ht="15.75" customHeight="1" s="19"/>
-    <row r="885" ht="15.75" customHeight="1" s="19"/>
-    <row r="886" ht="15.75" customHeight="1" s="19"/>
-    <row r="887" ht="15.75" customHeight="1" s="19"/>
-    <row r="888" ht="15.75" customHeight="1" s="19"/>
-    <row r="889" ht="15.75" customHeight="1" s="19"/>
-    <row r="890" ht="15.75" customHeight="1" s="19"/>
-    <row r="891" ht="15.75" customHeight="1" s="19"/>
-    <row r="892" ht="15.75" customHeight="1" s="19"/>
-    <row r="893" ht="15.75" customHeight="1" s="19"/>
-    <row r="894" ht="15.75" customHeight="1" s="19"/>
-    <row r="895" ht="15.75" customHeight="1" s="19"/>
-    <row r="896" ht="15.75" customHeight="1" s="19"/>
-    <row r="897" ht="15.75" customHeight="1" s="19"/>
-    <row r="898" ht="15.75" customHeight="1" s="19"/>
-    <row r="899" ht="15.75" customHeight="1" s="19"/>
-    <row r="900" ht="15.75" customHeight="1" s="19"/>
-    <row r="901" ht="15.75" customHeight="1" s="19"/>
-    <row r="902" ht="15.75" customHeight="1" s="19"/>
-    <row r="903" ht="15.75" customHeight="1" s="19"/>
-    <row r="904" ht="15.75" customHeight="1" s="19"/>
-    <row r="905" ht="15.75" customHeight="1" s="19"/>
-    <row r="906" ht="15.75" customHeight="1" s="19"/>
-    <row r="907" ht="15.75" customHeight="1" s="19"/>
-    <row r="908" ht="15.75" customHeight="1" s="19"/>
-    <row r="909" ht="15.75" customHeight="1" s="19"/>
-    <row r="910" ht="15.75" customHeight="1" s="19"/>
-    <row r="911" ht="15.75" customHeight="1" s="19"/>
-    <row r="912" ht="15.75" customHeight="1" s="19"/>
-    <row r="913" ht="15.75" customHeight="1" s="19"/>
-    <row r="914" ht="15.75" customHeight="1" s="19"/>
-    <row r="915" ht="15.75" customHeight="1" s="19"/>
-    <row r="916" ht="15.75" customHeight="1" s="19"/>
-    <row r="917" ht="15.75" customHeight="1" s="19"/>
-    <row r="918" ht="15.75" customHeight="1" s="19"/>
-    <row r="919" ht="15.75" customHeight="1" s="19"/>
-    <row r="920" ht="15.75" customHeight="1" s="19"/>
-    <row r="921" ht="15.75" customHeight="1" s="19"/>
-    <row r="922" ht="15.75" customHeight="1" s="19"/>
-    <row r="923" ht="15.75" customHeight="1" s="19"/>
-    <row r="924" ht="15.75" customHeight="1" s="19"/>
-    <row r="925" ht="15.75" customHeight="1" s="19"/>
-    <row r="926" ht="15.75" customHeight="1" s="19"/>
-    <row r="927" ht="15.75" customHeight="1" s="19"/>
-    <row r="928" ht="15.75" customHeight="1" s="19"/>
-    <row r="929" ht="15.75" customHeight="1" s="19"/>
-    <row r="930" ht="15.75" customHeight="1" s="19"/>
-    <row r="931" ht="15.75" customHeight="1" s="19"/>
-    <row r="932" ht="15.75" customHeight="1" s="19"/>
-    <row r="933" ht="15.75" customHeight="1" s="19"/>
-    <row r="934" ht="15.75" customHeight="1" s="19"/>
-    <row r="935" ht="15.75" customHeight="1" s="19"/>
-    <row r="936" ht="15.75" customHeight="1" s="19"/>
-    <row r="937" ht="15.75" customHeight="1" s="19"/>
-    <row r="938" ht="15.75" customHeight="1" s="19"/>
-    <row r="939" ht="15.75" customHeight="1" s="19"/>
-    <row r="940" ht="15.75" customHeight="1" s="19"/>
-    <row r="941" ht="15.75" customHeight="1" s="19"/>
-    <row r="942" ht="15.75" customHeight="1" s="19"/>
-    <row r="943" ht="15.75" customHeight="1" s="19"/>
-    <row r="944" ht="15.75" customHeight="1" s="19"/>
-    <row r="945" ht="15.75" customHeight="1" s="19"/>
-    <row r="946" ht="15.75" customHeight="1" s="19"/>
-    <row r="947" ht="15.75" customHeight="1" s="19"/>
-    <row r="948" ht="15.75" customHeight="1" s="19"/>
-    <row r="949" ht="15.75" customHeight="1" s="19"/>
-    <row r="950" ht="15.75" customHeight="1" s="19"/>
-    <row r="951" ht="15.75" customHeight="1" s="19"/>
-    <row r="952" ht="15.75" customHeight="1" s="19"/>
-    <row r="953" ht="15.75" customHeight="1" s="19"/>
-    <row r="954" ht="15.75" customHeight="1" s="19"/>
-    <row r="955" ht="15.75" customHeight="1" s="19"/>
-    <row r="956" ht="15.75" customHeight="1" s="19"/>
-    <row r="957" ht="15.75" customHeight="1" s="19"/>
-    <row r="958" ht="15.75" customHeight="1" s="19"/>
-    <row r="959" ht="15.75" customHeight="1" s="19"/>
-    <row r="960" ht="15.75" customHeight="1" s="19"/>
-    <row r="961" ht="15.75" customHeight="1" s="19"/>
-    <row r="962" ht="15.75" customHeight="1" s="19"/>
-    <row r="963" ht="15.75" customHeight="1" s="19"/>
-    <row r="964" ht="15.75" customHeight="1" s="19"/>
-    <row r="965" ht="15.75" customHeight="1" s="19"/>
-    <row r="966" ht="15.75" customHeight="1" s="19"/>
-    <row r="967" ht="15.75" customHeight="1" s="19"/>
-    <row r="968" ht="15.75" customHeight="1" s="19"/>
-    <row r="969" ht="15.75" customHeight="1" s="19"/>
-    <row r="970" ht="15.75" customHeight="1" s="19"/>
-    <row r="971" ht="15.75" customHeight="1" s="19"/>
-    <row r="972" ht="15.75" customHeight="1" s="19"/>
-    <row r="973" ht="15.75" customHeight="1" s="19"/>
-    <row r="974" ht="15.75" customHeight="1" s="19"/>
-    <row r="975" ht="15.75" customHeight="1" s="19"/>
-    <row r="976" ht="15.75" customHeight="1" s="19"/>
-    <row r="977" ht="15.75" customHeight="1" s="19"/>
-    <row r="978" ht="15.75" customHeight="1" s="19"/>
-    <row r="979" ht="15.75" customHeight="1" s="19"/>
-    <row r="980" ht="15.75" customHeight="1" s="19"/>
-    <row r="981" ht="15.75" customHeight="1" s="19"/>
-    <row r="982" ht="15.75" customHeight="1" s="19"/>
-    <row r="983" ht="15.75" customHeight="1" s="19"/>
-    <row r="984" ht="15.75" customHeight="1" s="19"/>
-    <row r="985" ht="15.75" customHeight="1" s="19"/>
-    <row r="986" ht="15.75" customHeight="1" s="19"/>
-    <row r="987" ht="15.75" customHeight="1" s="19"/>
-    <row r="988" ht="15.75" customHeight="1" s="19"/>
-    <row r="989" ht="15.75" customHeight="1" s="19"/>
-    <row r="990" ht="15.75" customHeight="1" s="19"/>
-    <row r="991" ht="15.75" customHeight="1" s="19"/>
-    <row r="992" ht="15.75" customHeight="1" s="19"/>
-    <row r="993" ht="15.75" customHeight="1" s="19"/>
-    <row r="994" ht="15.75" customHeight="1" s="19"/>
-    <row r="995" ht="15.75" customHeight="1" s="19"/>
-    <row r="996" ht="15.75" customHeight="1" s="19"/>
-    <row r="997" ht="15.75" customHeight="1" s="19"/>
-    <row r="998" ht="15.75" customHeight="1" s="19"/>
-    <row r="999" ht="15.75" customHeight="1" s="19"/>
-    <row r="1000" ht="15.75" customHeight="1" s="19"/>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.5" customHeight="1" s="19">
+      <c r="A2" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Written before the code (TDD, 2026-10-05), then walked through the running app on 2026-10-05 (all 20 cases, against the SPM62 fixtures): every label, message and page address in the cases is what the code shows. Entries marked DECIDED were chosen by the team rather than taken from the story; change them in code and cases together.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="71.5" customHeight="1" s="19">
+      <c r="A3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: who may edit (AC1, AC3). Only the coordinator assigned to the event. The organiser who raised it (after submission changes go through the coordinator, clarification #102), other coordinators, the Ops Manager, Venue Staff, Technical Support and Attendees may not.</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="n"/>
+    </row>
+    <row r="4" ht="179.5" customHeight="1" s="19">
+      <c r="A4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: the page is 'Edit event information' at /events/&lt;reference&gt;/update, reached from an 'Edit event information' button at the top of the event page (shown only to the assigned coordinator in those statuses). The organiser's draft editor at /events/&lt;reference&gt;/edit is unchanged. After saving, the form is replaced on the same page by a green alert 'Event information updated.' ('Event information updated. The event is back in Planning and needs to be confirmed again.' when the status reverted), what the save flagged (see 'who sees the flags'), and a 'Back to event' link. Refusal: red alert 'You can't edit this event's information' with 'Only the coordinator assigned to this event can change its information.' or 'Event information can only be changed while the event is Approved, Planning or Confirmed.', and a 'Back to event' button.</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="n"/>
+    </row>
+    <row r="5" ht="139" customHeight="1" s="19">
+      <c r="A5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: the permitted fields (AC1, AC3) are the organiser's request fields, with the same labels and validation messages as the draft form (S-08): Event name, Type of event, Purpose, Description, Starts at, Ends at, Expected attendance, Preferred room layout, The venue must have, Accessibility needs, Other accessibility notes and Anything else about the space. Not on the form: organiser, company, coordinator, status and reference; equipment, which is changed on the Equipment tab (SPM-47; the form says 'Equipment is changed on the Equipment tab.'); and the registration settings, which are Configure Event Registration's (SPM-64, see below).</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="139" customHeight="1" s="19">
+      <c r="A6" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: the important information (AC4) is: 'Date and time' (Starts at, Ends at), 'Expected attendance', 'Venue requirements' (Preferred room layout, The venue must have, Accessibility needs), and equipment requirements (changed on the Equipment tab). Everything else is ordinary, including Other accessibility notes and Anything else about the space (free text that venue matching does not read). A value changed and then changed back is not a change (TC12). As the form is edited, an amber alert 'These changes affect existing arrangements' reads 'You've changed: &lt;list&gt;. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="125.5" customHeight="1" s="19">
+      <c r="A7" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: reverting a Confirmed event (AC6). It reverts when a saved change flags a venue booking or an equipment request, which are the arrangements confirmation depends on (SPM-34). Before saving, a dialog 'Move this event back to Planning?' reads '&lt;title&gt; is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with 'Keep editing' and 'Save and move to Planning'. The event moves to Planning, Confirmed at is cleared, and a status history entry is written: 'Event information changed: Date and time' (the list of changes).</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="44.5" customHeight="1" s="19">
+      <c r="A8" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-10-05: editing information on an Approved event does not begin planning (TC03, TC04). Only venue and equipment actions do (SPM-54).</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="395.5" customHeight="1" s="19">
+      <c r="A9" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Fixture events: `scripts/seed-spm62.ts` (`npm run fixtures:spm62`) creates them with their bookings, equipment, registrations and required facility; prisma/seed.ts creates the same events only (appended last), so run the script once after a full reseed. All are coordinated by Daniel Tan, and each has a unique title. (1) 'SPM62 Harbour Leadership Summit': Planning, organiser Evelyn Chen, 17 Mar 2027 09:00–17:00, attendance 80, layout theatre, required 'Fixed ceiling projector', Approved booking Orchard Seminar Room (ORC-SEM), 4K Portable Projector × 2 Reserved, registration on with capacity 100, closing 15 Mar 2027 09:00 (two days before, as every seeded event's registration does), and 12 attendees registered. (2) 'SPM62 Kirana Supplier Day': Planning, organiser Faridah Aziz, 21 Apr 2027 10:00–16:00, attendance 60, Approved booking Changi Conference Centre (CBP-CONF), Handheld Wireless Mic × 4 Reserved, registration on with 8 registered. (3) 'SPM62 Bayu Energy Outlook': Approved, organiser Hakim Zulkifli, 12 May 2027 09:00–12:00, attendance 40, no arrangements, registration off. (4) 'SPM62 Anchorpoint Logistics Forum': Approved, organiser Melissa Yap, 18 May 2027 09:00–12:00, attendance 50, no arrangements. (5) 'SPM62 Straits Pharmacy Forum': Confirmed, organiser Evelyn Chen, 9 Jun 2027 09:00–17:00, attendance 120, Approved booking Marina Auditorium (MAR-AUD), Powered Speaker × 2 Reserved, registration on with capacity 150 and 20 registered. (6) 'SPM62 Meridian Quarterly Review': Confirmed, organiser James Koh, 16 Jun 2027 14:00–17:00, attendance 30, Approved booking Marina Boardroom 1 (MAR-BR1), registration off. (7) 'SPM62 Sundara Hospitality Showcase': Confirmed, organiser Dewi Kartika, 23 Jun 2027 10:00–18:00, attendance 70, Approved booking Orchard Gallery (ORC-GAL), no equipment. (8) 'SPM62 Civic Learning Day': Under review, organiser Grace Abdullah, 7 Jul 2027. (9) 'SPM62 Pearl Delta Plant Tour': Completed, organiser Samuel Ong, 10 Sep 2026.</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -16187,9 +15089,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC19</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC18</t>
         </is>
       </c>
     </row>
@@ -16199,7 +15101,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
@@ -16207,47 +15109,45 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="111.75" customHeight="1" s="19">
+    <row r="4" ht="98.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Click 'Edit event information'
-3. Change 'Expected attendance' to 0
-4. Click 'Save changes'
-5. Clear 'Expected attendance'
-6. Click 'Save changes'
-7. Click 'Cancel'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
+3. Clear 'Event name'
+4. Change 'Ends at' to 17 Mar 2027, 08:00
+5. Click 'Save changes'
+6. Click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit | Expected attendance: 0, then blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit | Event name: (blank) | Starts at: 17 Mar 2027, 09:00 | Ends at: 17 Mar 2027, 08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
-Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
-Step 7: The event page shows 'Expected attendance' '80'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time', because Ends at was changed.
+Step 6: The event page shows the title 'SPM62 Harbour Leadership Summit' and 'When' '17 Mar 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -16257,7 +15157,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16289,11 +15189,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
-Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
-Step 7: The event page shows 'Expected attendance' '80'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 5: Nothing is saved and no dialog appears. 'Give the event a name so you can find it again.' is shown in red under 'Event name', and 'Ends at must be after starts at.' is shown in red under 'Ends at'. The cursor moves to 'Event name'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time', because Ends at was changed.
+Step 6: The event page shows the title 'SPM62 Harbour Leadership Summit' and 'When' '17 Mar 2027, 09:00–17:00'.</t>
         </is>
       </c>
     </row>
@@ -16327,7 +15226,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16357,11 +15256,14 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
-Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
-Step 7: The event page shows 'Expected attendance' '80'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
+2. Click 'Edit event information'
+3. Clear 'Event name'
+4. Change 'Ends at' to 17 Mar 2027, 08:00
+5. Click 'Save changes'
+6. Click 'Cancel'</t>
         </is>
       </c>
     </row>
@@ -16395,7 +15297,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -17424,9 +16326,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC20</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC19</t>
         </is>
       </c>
     </row>
@@ -17436,7 +16338,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
@@ -17444,13 +16346,1250 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="111.75" customHeight="1" s="19">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
+2. Click 'Edit event information'
+3. Change 'Expected attendance' to 0
+4. Click 'Save changes'
+5. Clear 'Expected attendance'
+6. Click 'Save changes'
+7. Click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit | Expected attendance: 0, then blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111.75" customHeight="1" s="19">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
+Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
+Step 7: The event page shows 'Expected attendance' '80'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="19">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="19">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19"/>
+    <row r="10" ht="15.75" customHeight="1" s="19">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
+Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
+Step 7: The event page shows 'Expected attendance' '80'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="19">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="19">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="19">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="19">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: Nothing is saved. 'Enter a whole number of people, at least 1.' is shown in red under 'Expected attendance'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Expected attendance'.
+Step 6: Nothing is saved. 'Enter how many people you expect.' is shown in red under 'Expected attendance'. The amber alert still lists 'Expected attendance'.
+Step 7: The event page shows 'Expected attendance' '80'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="19">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="19">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="19"/>
+    <row r="23" ht="15.75" customHeight="1" s="19"/>
+    <row r="24" ht="15.75" customHeight="1" s="19"/>
+    <row r="25" ht="15.75" customHeight="1" s="19"/>
+    <row r="26" ht="15.75" customHeight="1" s="19"/>
+    <row r="27" ht="15.75" customHeight="1" s="19"/>
+    <row r="28" ht="15.75" customHeight="1" s="19"/>
+    <row r="29" ht="15.75" customHeight="1" s="19"/>
+    <row r="30" ht="15.75" customHeight="1" s="19"/>
+    <row r="31" ht="15.75" customHeight="1" s="19"/>
+    <row r="32" ht="15.75" customHeight="1" s="19"/>
+    <row r="33" ht="15.75" customHeight="1" s="19"/>
+    <row r="34" ht="15.75" customHeight="1" s="19"/>
+    <row r="35" ht="15.75" customHeight="1" s="19"/>
+    <row r="36" ht="15.75" customHeight="1" s="19"/>
+    <row r="37" ht="15.75" customHeight="1" s="19"/>
+    <row r="38" ht="15.75" customHeight="1" s="19"/>
+    <row r="39" ht="15.75" customHeight="1" s="19"/>
+    <row r="40" ht="15.75" customHeight="1" s="19"/>
+    <row r="41" ht="15.75" customHeight="1" s="19"/>
+    <row r="42" ht="15.75" customHeight="1" s="19"/>
+    <row r="43" ht="15.75" customHeight="1" s="19"/>
+    <row r="44" ht="15.75" customHeight="1" s="19"/>
+    <row r="45" ht="15.75" customHeight="1" s="19"/>
+    <row r="46" ht="15.75" customHeight="1" s="19"/>
+    <row r="47" ht="15.75" customHeight="1" s="19"/>
+    <row r="48" ht="15.75" customHeight="1" s="19"/>
+    <row r="49" ht="15.75" customHeight="1" s="19"/>
+    <row r="50" ht="15.75" customHeight="1" s="19"/>
+    <row r="51" ht="15.75" customHeight="1" s="19"/>
+    <row r="52" ht="15.75" customHeight="1" s="19"/>
+    <row r="53" ht="15.75" customHeight="1" s="19"/>
+    <row r="54" ht="15.75" customHeight="1" s="19"/>
+    <row r="55" ht="15.75" customHeight="1" s="19"/>
+    <row r="56" ht="15.75" customHeight="1" s="19"/>
+    <row r="57" ht="15.75" customHeight="1" s="19"/>
+    <row r="58" ht="15.75" customHeight="1" s="19"/>
+    <row r="59" ht="15.75" customHeight="1" s="19"/>
+    <row r="60" ht="15.75" customHeight="1" s="19"/>
+    <row r="61" ht="15.75" customHeight="1" s="19"/>
+    <row r="62" ht="15.75" customHeight="1" s="19"/>
+    <row r="63" ht="15.75" customHeight="1" s="19"/>
+    <row r="64" ht="15.75" customHeight="1" s="19"/>
+    <row r="65" ht="15.75" customHeight="1" s="19"/>
+    <row r="66" ht="15.75" customHeight="1" s="19"/>
+    <row r="67" ht="15.75" customHeight="1" s="19"/>
+    <row r="68" ht="15.75" customHeight="1" s="19"/>
+    <row r="69" ht="15.75" customHeight="1" s="19"/>
+    <row r="70" ht="15.75" customHeight="1" s="19"/>
+    <row r="71" ht="15.75" customHeight="1" s="19"/>
+    <row r="72" ht="15.75" customHeight="1" s="19"/>
+    <row r="73" ht="15.75" customHeight="1" s="19"/>
+    <row r="74" ht="15.75" customHeight="1" s="19"/>
+    <row r="75" ht="15.75" customHeight="1" s="19"/>
+    <row r="76" ht="15.75" customHeight="1" s="19"/>
+    <row r="77" ht="15.75" customHeight="1" s="19"/>
+    <row r="78" ht="15.75" customHeight="1" s="19"/>
+    <row r="79" ht="15.75" customHeight="1" s="19"/>
+    <row r="80" ht="15.75" customHeight="1" s="19"/>
+    <row r="81" ht="15.75" customHeight="1" s="19"/>
+    <row r="82" ht="15.75" customHeight="1" s="19"/>
+    <row r="83" ht="15.75" customHeight="1" s="19"/>
+    <row r="84" ht="15.75" customHeight="1" s="19"/>
+    <row r="85" ht="15.75" customHeight="1" s="19"/>
+    <row r="86" ht="15.75" customHeight="1" s="19"/>
+    <row r="87" ht="15.75" customHeight="1" s="19"/>
+    <row r="88" ht="15.75" customHeight="1" s="19"/>
+    <row r="89" ht="15.75" customHeight="1" s="19"/>
+    <row r="90" ht="15.75" customHeight="1" s="19"/>
+    <row r="91" ht="15.75" customHeight="1" s="19"/>
+    <row r="92" ht="15.75" customHeight="1" s="19"/>
+    <row r="93" ht="15.75" customHeight="1" s="19"/>
+    <row r="94" ht="15.75" customHeight="1" s="19"/>
+    <row r="95" ht="15.75" customHeight="1" s="19"/>
+    <row r="96" ht="15.75" customHeight="1" s="19"/>
+    <row r="97" ht="15.75" customHeight="1" s="19"/>
+    <row r="98" ht="15.75" customHeight="1" s="19"/>
+    <row r="99" ht="15.75" customHeight="1" s="19"/>
+    <row r="100" ht="15.75" customHeight="1" s="19"/>
+    <row r="101" ht="15.75" customHeight="1" s="19"/>
+    <row r="102" ht="15.75" customHeight="1" s="19"/>
+    <row r="103" ht="15.75" customHeight="1" s="19"/>
+    <row r="104" ht="15.75" customHeight="1" s="19"/>
+    <row r="105" ht="15.75" customHeight="1" s="19"/>
+    <row r="106" ht="15.75" customHeight="1" s="19"/>
+    <row r="107" ht="15.75" customHeight="1" s="19"/>
+    <row r="108" ht="15.75" customHeight="1" s="19"/>
+    <row r="109" ht="15.75" customHeight="1" s="19"/>
+    <row r="110" ht="15.75" customHeight="1" s="19"/>
+    <row r="111" ht="15.75" customHeight="1" s="19"/>
+    <row r="112" ht="15.75" customHeight="1" s="19"/>
+    <row r="113" ht="15.75" customHeight="1" s="19"/>
+    <row r="114" ht="15.75" customHeight="1" s="19"/>
+    <row r="115" ht="15.75" customHeight="1" s="19"/>
+    <row r="116" ht="15.75" customHeight="1" s="19"/>
+    <row r="117" ht="15.75" customHeight="1" s="19"/>
+    <row r="118" ht="15.75" customHeight="1" s="19"/>
+    <row r="119" ht="15.75" customHeight="1" s="19"/>
+    <row r="120" ht="15.75" customHeight="1" s="19"/>
+    <row r="121" ht="15.75" customHeight="1" s="19"/>
+    <row r="122" ht="15.75" customHeight="1" s="19"/>
+    <row r="123" ht="15.75" customHeight="1" s="19"/>
+    <row r="124" ht="15.75" customHeight="1" s="19"/>
+    <row r="125" ht="15.75" customHeight="1" s="19"/>
+    <row r="126" ht="15.75" customHeight="1" s="19"/>
+    <row r="127" ht="15.75" customHeight="1" s="19"/>
+    <row r="128" ht="15.75" customHeight="1" s="19"/>
+    <row r="129" ht="15.75" customHeight="1" s="19"/>
+    <row r="130" ht="15.75" customHeight="1" s="19"/>
+    <row r="131" ht="15.75" customHeight="1" s="19"/>
+    <row r="132" ht="15.75" customHeight="1" s="19"/>
+    <row r="133" ht="15.75" customHeight="1" s="19"/>
+    <row r="134" ht="15.75" customHeight="1" s="19"/>
+    <row r="135" ht="15.75" customHeight="1" s="19"/>
+    <row r="136" ht="15.75" customHeight="1" s="19"/>
+    <row r="137" ht="15.75" customHeight="1" s="19"/>
+    <row r="138" ht="15.75" customHeight="1" s="19"/>
+    <row r="139" ht="15.75" customHeight="1" s="19"/>
+    <row r="140" ht="15.75" customHeight="1" s="19"/>
+    <row r="141" ht="15.75" customHeight="1" s="19"/>
+    <row r="142" ht="15.75" customHeight="1" s="19"/>
+    <row r="143" ht="15.75" customHeight="1" s="19"/>
+    <row r="144" ht="15.75" customHeight="1" s="19"/>
+    <row r="145" ht="15.75" customHeight="1" s="19"/>
+    <row r="146" ht="15.75" customHeight="1" s="19"/>
+    <row r="147" ht="15.75" customHeight="1" s="19"/>
+    <row r="148" ht="15.75" customHeight="1" s="19"/>
+    <row r="149" ht="15.75" customHeight="1" s="19"/>
+    <row r="150" ht="15.75" customHeight="1" s="19"/>
+    <row r="151" ht="15.75" customHeight="1" s="19"/>
+    <row r="152" ht="15.75" customHeight="1" s="19"/>
+    <row r="153" ht="15.75" customHeight="1" s="19"/>
+    <row r="154" ht="15.75" customHeight="1" s="19"/>
+    <row r="155" ht="15.75" customHeight="1" s="19"/>
+    <row r="156" ht="15.75" customHeight="1" s="19"/>
+    <row r="157" ht="15.75" customHeight="1" s="19"/>
+    <row r="158" ht="15.75" customHeight="1" s="19"/>
+    <row r="159" ht="15.75" customHeight="1" s="19"/>
+    <row r="160" ht="15.75" customHeight="1" s="19"/>
+    <row r="161" ht="15.75" customHeight="1" s="19"/>
+    <row r="162" ht="15.75" customHeight="1" s="19"/>
+    <row r="163" ht="15.75" customHeight="1" s="19"/>
+    <row r="164" ht="15.75" customHeight="1" s="19"/>
+    <row r="165" ht="15.75" customHeight="1" s="19"/>
+    <row r="166" ht="15.75" customHeight="1" s="19"/>
+    <row r="167" ht="15.75" customHeight="1" s="19"/>
+    <row r="168" ht="15.75" customHeight="1" s="19"/>
+    <row r="169" ht="15.75" customHeight="1" s="19"/>
+    <row r="170" ht="15.75" customHeight="1" s="19"/>
+    <row r="171" ht="15.75" customHeight="1" s="19"/>
+    <row r="172" ht="15.75" customHeight="1" s="19"/>
+    <row r="173" ht="15.75" customHeight="1" s="19"/>
+    <row r="174" ht="15.75" customHeight="1" s="19"/>
+    <row r="175" ht="15.75" customHeight="1" s="19"/>
+    <row r="176" ht="15.75" customHeight="1" s="19"/>
+    <row r="177" ht="15.75" customHeight="1" s="19"/>
+    <row r="178" ht="15.75" customHeight="1" s="19"/>
+    <row r="179" ht="15.75" customHeight="1" s="19"/>
+    <row r="180" ht="15.75" customHeight="1" s="19"/>
+    <row r="181" ht="15.75" customHeight="1" s="19"/>
+    <row r="182" ht="15.75" customHeight="1" s="19"/>
+    <row r="183" ht="15.75" customHeight="1" s="19"/>
+    <row r="184" ht="15.75" customHeight="1" s="19"/>
+    <row r="185" ht="15.75" customHeight="1" s="19"/>
+    <row r="186" ht="15.75" customHeight="1" s="19"/>
+    <row r="187" ht="15.75" customHeight="1" s="19"/>
+    <row r="188" ht="15.75" customHeight="1" s="19"/>
+    <row r="189" ht="15.75" customHeight="1" s="19"/>
+    <row r="190" ht="15.75" customHeight="1" s="19"/>
+    <row r="191" ht="15.75" customHeight="1" s="19"/>
+    <row r="192" ht="15.75" customHeight="1" s="19"/>
+    <row r="193" ht="15.75" customHeight="1" s="19"/>
+    <row r="194" ht="15.75" customHeight="1" s="19"/>
+    <row r="195" ht="15.75" customHeight="1" s="19"/>
+    <row r="196" ht="15.75" customHeight="1" s="19"/>
+    <row r="197" ht="15.75" customHeight="1" s="19"/>
+    <row r="198" ht="15.75" customHeight="1" s="19"/>
+    <row r="199" ht="15.75" customHeight="1" s="19"/>
+    <row r="200" ht="15.75" customHeight="1" s="19"/>
+    <row r="201" ht="15.75" customHeight="1" s="19"/>
+    <row r="202" ht="15.75" customHeight="1" s="19"/>
+    <row r="203" ht="15.75" customHeight="1" s="19"/>
+    <row r="204" ht="15.75" customHeight="1" s="19"/>
+    <row r="205" ht="15.75" customHeight="1" s="19"/>
+    <row r="206" ht="15.75" customHeight="1" s="19"/>
+    <row r="207" ht="15.75" customHeight="1" s="19"/>
+    <row r="208" ht="15.75" customHeight="1" s="19"/>
+    <row r="209" ht="15.75" customHeight="1" s="19"/>
+    <row r="210" ht="15.75" customHeight="1" s="19"/>
+    <row r="211" ht="15.75" customHeight="1" s="19"/>
+    <row r="212" ht="15.75" customHeight="1" s="19"/>
+    <row r="213" ht="15.75" customHeight="1" s="19"/>
+    <row r="214" ht="15.75" customHeight="1" s="19"/>
+    <row r="215" ht="15.75" customHeight="1" s="19"/>
+    <row r="216" ht="15.75" customHeight="1" s="19"/>
+    <row r="217" ht="15.75" customHeight="1" s="19"/>
+    <row r="218" ht="15.75" customHeight="1" s="19"/>
+    <row r="219" ht="15.75" customHeight="1" s="19"/>
+    <row r="220" ht="15.75" customHeight="1" s="19"/>
+    <row r="221" ht="15.75" customHeight="1" s="19"/>
+    <row r="222" ht="15.75" customHeight="1" s="19"/>
+    <row r="223" ht="15.75" customHeight="1" s="19"/>
+    <row r="224" ht="15.75" customHeight="1" s="19"/>
+    <row r="225" ht="15.75" customHeight="1" s="19"/>
+    <row r="226" ht="15.75" customHeight="1" s="19"/>
+    <row r="227" ht="15.75" customHeight="1" s="19"/>
+    <row r="228" ht="15.75" customHeight="1" s="19"/>
+    <row r="229" ht="15.75" customHeight="1" s="19"/>
+    <row r="230" ht="15.75" customHeight="1" s="19"/>
+    <row r="231" ht="15.75" customHeight="1" s="19"/>
+    <row r="232" ht="15.75" customHeight="1" s="19"/>
+    <row r="233" ht="15.75" customHeight="1" s="19"/>
+    <row r="234" ht="15.75" customHeight="1" s="19"/>
+    <row r="235" ht="15.75" customHeight="1" s="19"/>
+    <row r="236" ht="15.75" customHeight="1" s="19"/>
+    <row r="237" ht="15.75" customHeight="1" s="19"/>
+    <row r="238" ht="15.75" customHeight="1" s="19"/>
+    <row r="239" ht="15.75" customHeight="1" s="19"/>
+    <row r="240" ht="15.75" customHeight="1" s="19"/>
+    <row r="241" ht="15.75" customHeight="1" s="19"/>
+    <row r="242" ht="15.75" customHeight="1" s="19"/>
+    <row r="243" ht="15.75" customHeight="1" s="19"/>
+    <row r="244" ht="15.75" customHeight="1" s="19"/>
+    <row r="245" ht="15.75" customHeight="1" s="19"/>
+    <row r="246" ht="15.75" customHeight="1" s="19"/>
+    <row r="247" ht="15.75" customHeight="1" s="19"/>
+    <row r="248" ht="15.75" customHeight="1" s="19"/>
+    <row r="249" ht="15.75" customHeight="1" s="19"/>
+    <row r="250" ht="15.75" customHeight="1" s="19"/>
+    <row r="251" ht="15.75" customHeight="1" s="19"/>
+    <row r="252" ht="15.75" customHeight="1" s="19"/>
+    <row r="253" ht="15.75" customHeight="1" s="19"/>
+    <row r="254" ht="15.75" customHeight="1" s="19"/>
+    <row r="255" ht="15.75" customHeight="1" s="19"/>
+    <row r="256" ht="15.75" customHeight="1" s="19"/>
+    <row r="257" ht="15.75" customHeight="1" s="19"/>
+    <row r="258" ht="15.75" customHeight="1" s="19"/>
+    <row r="259" ht="15.75" customHeight="1" s="19"/>
+    <row r="260" ht="15.75" customHeight="1" s="19"/>
+    <row r="261" ht="15.75" customHeight="1" s="19"/>
+    <row r="262" ht="15.75" customHeight="1" s="19"/>
+    <row r="263" ht="15.75" customHeight="1" s="19"/>
+    <row r="264" ht="15.75" customHeight="1" s="19"/>
+    <row r="265" ht="15.75" customHeight="1" s="19"/>
+    <row r="266" ht="15.75" customHeight="1" s="19"/>
+    <row r="267" ht="15.75" customHeight="1" s="19"/>
+    <row r="268" ht="15.75" customHeight="1" s="19"/>
+    <row r="269" ht="15.75" customHeight="1" s="19"/>
+    <row r="270" ht="15.75" customHeight="1" s="19"/>
+    <row r="271" ht="15.75" customHeight="1" s="19"/>
+    <row r="272" ht="15.75" customHeight="1" s="19"/>
+    <row r="273" ht="15.75" customHeight="1" s="19"/>
+    <row r="274" ht="15.75" customHeight="1" s="19"/>
+    <row r="275" ht="15.75" customHeight="1" s="19"/>
+    <row r="276" ht="15.75" customHeight="1" s="19"/>
+    <row r="277" ht="15.75" customHeight="1" s="19"/>
+    <row r="278" ht="15.75" customHeight="1" s="19"/>
+    <row r="279" ht="15.75" customHeight="1" s="19"/>
+    <row r="280" ht="15.75" customHeight="1" s="19"/>
+    <row r="281" ht="15.75" customHeight="1" s="19"/>
+    <row r="282" ht="15.75" customHeight="1" s="19"/>
+    <row r="283" ht="15.75" customHeight="1" s="19"/>
+    <row r="284" ht="15.75" customHeight="1" s="19"/>
+    <row r="285" ht="15.75" customHeight="1" s="19"/>
+    <row r="286" ht="15.75" customHeight="1" s="19"/>
+    <row r="287" ht="15.75" customHeight="1" s="19"/>
+    <row r="288" ht="15.75" customHeight="1" s="19"/>
+    <row r="289" ht="15.75" customHeight="1" s="19"/>
+    <row r="290" ht="15.75" customHeight="1" s="19"/>
+    <row r="291" ht="15.75" customHeight="1" s="19"/>
+    <row r="292" ht="15.75" customHeight="1" s="19"/>
+    <row r="293" ht="15.75" customHeight="1" s="19"/>
+    <row r="294" ht="15.75" customHeight="1" s="19"/>
+    <row r="295" ht="15.75" customHeight="1" s="19"/>
+    <row r="296" ht="15.75" customHeight="1" s="19"/>
+    <row r="297" ht="15.75" customHeight="1" s="19"/>
+    <row r="298" ht="15.75" customHeight="1" s="19"/>
+    <row r="299" ht="15.75" customHeight="1" s="19"/>
+    <row r="300" ht="15.75" customHeight="1" s="19"/>
+    <row r="301" ht="15.75" customHeight="1" s="19"/>
+    <row r="302" ht="15.75" customHeight="1" s="19"/>
+    <row r="303" ht="15.75" customHeight="1" s="19"/>
+    <row r="304" ht="15.75" customHeight="1" s="19"/>
+    <row r="305" ht="15.75" customHeight="1" s="19"/>
+    <row r="306" ht="15.75" customHeight="1" s="19"/>
+    <row r="307" ht="15.75" customHeight="1" s="19"/>
+    <row r="308" ht="15.75" customHeight="1" s="19"/>
+    <row r="309" ht="15.75" customHeight="1" s="19"/>
+    <row r="310" ht="15.75" customHeight="1" s="19"/>
+    <row r="311" ht="15.75" customHeight="1" s="19"/>
+    <row r="312" ht="15.75" customHeight="1" s="19"/>
+    <row r="313" ht="15.75" customHeight="1" s="19"/>
+    <row r="314" ht="15.75" customHeight="1" s="19"/>
+    <row r="315" ht="15.75" customHeight="1" s="19"/>
+    <row r="316" ht="15.75" customHeight="1" s="19"/>
+    <row r="317" ht="15.75" customHeight="1" s="19"/>
+    <row r="318" ht="15.75" customHeight="1" s="19"/>
+    <row r="319" ht="15.75" customHeight="1" s="19"/>
+    <row r="320" ht="15.75" customHeight="1" s="19"/>
+    <row r="321" ht="15.75" customHeight="1" s="19"/>
+    <row r="322" ht="15.75" customHeight="1" s="19"/>
+    <row r="323" ht="15.75" customHeight="1" s="19"/>
+    <row r="324" ht="15.75" customHeight="1" s="19"/>
+    <row r="325" ht="15.75" customHeight="1" s="19"/>
+    <row r="326" ht="15.75" customHeight="1" s="19"/>
+    <row r="327" ht="15.75" customHeight="1" s="19"/>
+    <row r="328" ht="15.75" customHeight="1" s="19"/>
+    <row r="329" ht="15.75" customHeight="1" s="19"/>
+    <row r="330" ht="15.75" customHeight="1" s="19"/>
+    <row r="331" ht="15.75" customHeight="1" s="19"/>
+    <row r="332" ht="15.75" customHeight="1" s="19"/>
+    <row r="333" ht="15.75" customHeight="1" s="19"/>
+    <row r="334" ht="15.75" customHeight="1" s="19"/>
+    <row r="335" ht="15.75" customHeight="1" s="19"/>
+    <row r="336" ht="15.75" customHeight="1" s="19"/>
+    <row r="337" ht="15.75" customHeight="1" s="19"/>
+    <row r="338" ht="15.75" customHeight="1" s="19"/>
+    <row r="339" ht="15.75" customHeight="1" s="19"/>
+    <row r="340" ht="15.75" customHeight="1" s="19"/>
+    <row r="341" ht="15.75" customHeight="1" s="19"/>
+    <row r="342" ht="15.75" customHeight="1" s="19"/>
+    <row r="343" ht="15.75" customHeight="1" s="19"/>
+    <row r="344" ht="15.75" customHeight="1" s="19"/>
+    <row r="345" ht="15.75" customHeight="1" s="19"/>
+    <row r="346" ht="15.75" customHeight="1" s="19"/>
+    <row r="347" ht="15.75" customHeight="1" s="19"/>
+    <row r="348" ht="15.75" customHeight="1" s="19"/>
+    <row r="349" ht="15.75" customHeight="1" s="19"/>
+    <row r="350" ht="15.75" customHeight="1" s="19"/>
+    <row r="351" ht="15.75" customHeight="1" s="19"/>
+    <row r="352" ht="15.75" customHeight="1" s="19"/>
+    <row r="353" ht="15.75" customHeight="1" s="19"/>
+    <row r="354" ht="15.75" customHeight="1" s="19"/>
+    <row r="355" ht="15.75" customHeight="1" s="19"/>
+    <row r="356" ht="15.75" customHeight="1" s="19"/>
+    <row r="357" ht="15.75" customHeight="1" s="19"/>
+    <row r="358" ht="15.75" customHeight="1" s="19"/>
+    <row r="359" ht="15.75" customHeight="1" s="19"/>
+    <row r="360" ht="15.75" customHeight="1" s="19"/>
+    <row r="361" ht="15.75" customHeight="1" s="19"/>
+    <row r="362" ht="15.75" customHeight="1" s="19"/>
+    <row r="363" ht="15.75" customHeight="1" s="19"/>
+    <row r="364" ht="15.75" customHeight="1" s="19"/>
+    <row r="365" ht="15.75" customHeight="1" s="19"/>
+    <row r="366" ht="15.75" customHeight="1" s="19"/>
+    <row r="367" ht="15.75" customHeight="1" s="19"/>
+    <row r="368" ht="15.75" customHeight="1" s="19"/>
+    <row r="369" ht="15.75" customHeight="1" s="19"/>
+    <row r="370" ht="15.75" customHeight="1" s="19"/>
+    <row r="371" ht="15.75" customHeight="1" s="19"/>
+    <row r="372" ht="15.75" customHeight="1" s="19"/>
+    <row r="373" ht="15.75" customHeight="1" s="19"/>
+    <row r="374" ht="15.75" customHeight="1" s="19"/>
+    <row r="375" ht="15.75" customHeight="1" s="19"/>
+    <row r="376" ht="15.75" customHeight="1" s="19"/>
+    <row r="377" ht="15.75" customHeight="1" s="19"/>
+    <row r="378" ht="15.75" customHeight="1" s="19"/>
+    <row r="379" ht="15.75" customHeight="1" s="19"/>
+    <row r="380" ht="15.75" customHeight="1" s="19"/>
+    <row r="381" ht="15.75" customHeight="1" s="19"/>
+    <row r="382" ht="15.75" customHeight="1" s="19"/>
+    <row r="383" ht="15.75" customHeight="1" s="19"/>
+    <row r="384" ht="15.75" customHeight="1" s="19"/>
+    <row r="385" ht="15.75" customHeight="1" s="19"/>
+    <row r="386" ht="15.75" customHeight="1" s="19"/>
+    <row r="387" ht="15.75" customHeight="1" s="19"/>
+    <row r="388" ht="15.75" customHeight="1" s="19"/>
+    <row r="389" ht="15.75" customHeight="1" s="19"/>
+    <row r="390" ht="15.75" customHeight="1" s="19"/>
+    <row r="391" ht="15.75" customHeight="1" s="19"/>
+    <row r="392" ht="15.75" customHeight="1" s="19"/>
+    <row r="393" ht="15.75" customHeight="1" s="19"/>
+    <row r="394" ht="15.75" customHeight="1" s="19"/>
+    <row r="395" ht="15.75" customHeight="1" s="19"/>
+    <row r="396" ht="15.75" customHeight="1" s="19"/>
+    <row r="397" ht="15.75" customHeight="1" s="19"/>
+    <row r="398" ht="15.75" customHeight="1" s="19"/>
+    <row r="399" ht="15.75" customHeight="1" s="19"/>
+    <row r="400" ht="15.75" customHeight="1" s="19"/>
+    <row r="401" ht="15.75" customHeight="1" s="19"/>
+    <row r="402" ht="15.75" customHeight="1" s="19"/>
+    <row r="403" ht="15.75" customHeight="1" s="19"/>
+    <row r="404" ht="15.75" customHeight="1" s="19"/>
+    <row r="405" ht="15.75" customHeight="1" s="19"/>
+    <row r="406" ht="15.75" customHeight="1" s="19"/>
+    <row r="407" ht="15.75" customHeight="1" s="19"/>
+    <row r="408" ht="15.75" customHeight="1" s="19"/>
+    <row r="409" ht="15.75" customHeight="1" s="19"/>
+    <row r="410" ht="15.75" customHeight="1" s="19"/>
+    <row r="411" ht="15.75" customHeight="1" s="19"/>
+    <row r="412" ht="15.75" customHeight="1" s="19"/>
+    <row r="413" ht="15.75" customHeight="1" s="19"/>
+    <row r="414" ht="15.75" customHeight="1" s="19"/>
+    <row r="415" ht="15.75" customHeight="1" s="19"/>
+    <row r="416" ht="15.75" customHeight="1" s="19"/>
+    <row r="417" ht="15.75" customHeight="1" s="19"/>
+    <row r="418" ht="15.75" customHeight="1" s="19"/>
+    <row r="419" ht="15.75" customHeight="1" s="19"/>
+    <row r="420" ht="15.75" customHeight="1" s="19"/>
+    <row r="421" ht="15.75" customHeight="1" s="19"/>
+    <row r="422" ht="15.75" customHeight="1" s="19"/>
+    <row r="423" ht="15.75" customHeight="1" s="19"/>
+    <row r="424" ht="15.75" customHeight="1" s="19"/>
+    <row r="425" ht="15.75" customHeight="1" s="19"/>
+    <row r="426" ht="15.75" customHeight="1" s="19"/>
+    <row r="427" ht="15.75" customHeight="1" s="19"/>
+    <row r="428" ht="15.75" customHeight="1" s="19"/>
+    <row r="429" ht="15.75" customHeight="1" s="19"/>
+    <row r="430" ht="15.75" customHeight="1" s="19"/>
+    <row r="431" ht="15.75" customHeight="1" s="19"/>
+    <row r="432" ht="15.75" customHeight="1" s="19"/>
+    <row r="433" ht="15.75" customHeight="1" s="19"/>
+    <row r="434" ht="15.75" customHeight="1" s="19"/>
+    <row r="435" ht="15.75" customHeight="1" s="19"/>
+    <row r="436" ht="15.75" customHeight="1" s="19"/>
+    <row r="437" ht="15.75" customHeight="1" s="19"/>
+    <row r="438" ht="15.75" customHeight="1" s="19"/>
+    <row r="439" ht="15.75" customHeight="1" s="19"/>
+    <row r="440" ht="15.75" customHeight="1" s="19"/>
+    <row r="441" ht="15.75" customHeight="1" s="19"/>
+    <row r="442" ht="15.75" customHeight="1" s="19"/>
+    <row r="443" ht="15.75" customHeight="1" s="19"/>
+    <row r="444" ht="15.75" customHeight="1" s="19"/>
+    <row r="445" ht="15.75" customHeight="1" s="19"/>
+    <row r="446" ht="15.75" customHeight="1" s="19"/>
+    <row r="447" ht="15.75" customHeight="1" s="19"/>
+    <row r="448" ht="15.75" customHeight="1" s="19"/>
+    <row r="449" ht="15.75" customHeight="1" s="19"/>
+    <row r="450" ht="15.75" customHeight="1" s="19"/>
+    <row r="451" ht="15.75" customHeight="1" s="19"/>
+    <row r="452" ht="15.75" customHeight="1" s="19"/>
+    <row r="453" ht="15.75" customHeight="1" s="19"/>
+    <row r="454" ht="15.75" customHeight="1" s="19"/>
+    <row r="455" ht="15.75" customHeight="1" s="19"/>
+    <row r="456" ht="15.75" customHeight="1" s="19"/>
+    <row r="457" ht="15.75" customHeight="1" s="19"/>
+    <row r="458" ht="15.75" customHeight="1" s="19"/>
+    <row r="459" ht="15.75" customHeight="1" s="19"/>
+    <row r="460" ht="15.75" customHeight="1" s="19"/>
+    <row r="461" ht="15.75" customHeight="1" s="19"/>
+    <row r="462" ht="15.75" customHeight="1" s="19"/>
+    <row r="463" ht="15.75" customHeight="1" s="19"/>
+    <row r="464" ht="15.75" customHeight="1" s="19"/>
+    <row r="465" ht="15.75" customHeight="1" s="19"/>
+    <row r="466" ht="15.75" customHeight="1" s="19"/>
+    <row r="467" ht="15.75" customHeight="1" s="19"/>
+    <row r="468" ht="15.75" customHeight="1" s="19"/>
+    <row r="469" ht="15.75" customHeight="1" s="19"/>
+    <row r="470" ht="15.75" customHeight="1" s="19"/>
+    <row r="471" ht="15.75" customHeight="1" s="19"/>
+    <row r="472" ht="15.75" customHeight="1" s="19"/>
+    <row r="473" ht="15.75" customHeight="1" s="19"/>
+    <row r="474" ht="15.75" customHeight="1" s="19"/>
+    <row r="475" ht="15.75" customHeight="1" s="19"/>
+    <row r="476" ht="15.75" customHeight="1" s="19"/>
+    <row r="477" ht="15.75" customHeight="1" s="19"/>
+    <row r="478" ht="15.75" customHeight="1" s="19"/>
+    <row r="479" ht="15.75" customHeight="1" s="19"/>
+    <row r="480" ht="15.75" customHeight="1" s="19"/>
+    <row r="481" ht="15.75" customHeight="1" s="19"/>
+    <row r="482" ht="15.75" customHeight="1" s="19"/>
+    <row r="483" ht="15.75" customHeight="1" s="19"/>
+    <row r="484" ht="15.75" customHeight="1" s="19"/>
+    <row r="485" ht="15.75" customHeight="1" s="19"/>
+    <row r="486" ht="15.75" customHeight="1" s="19"/>
+    <row r="487" ht="15.75" customHeight="1" s="19"/>
+    <row r="488" ht="15.75" customHeight="1" s="19"/>
+    <row r="489" ht="15.75" customHeight="1" s="19"/>
+    <row r="490" ht="15.75" customHeight="1" s="19"/>
+    <row r="491" ht="15.75" customHeight="1" s="19"/>
+    <row r="492" ht="15.75" customHeight="1" s="19"/>
+    <row r="493" ht="15.75" customHeight="1" s="19"/>
+    <row r="494" ht="15.75" customHeight="1" s="19"/>
+    <row r="495" ht="15.75" customHeight="1" s="19"/>
+    <row r="496" ht="15.75" customHeight="1" s="19"/>
+    <row r="497" ht="15.75" customHeight="1" s="19"/>
+    <row r="498" ht="15.75" customHeight="1" s="19"/>
+    <row r="499" ht="15.75" customHeight="1" s="19"/>
+    <row r="500" ht="15.75" customHeight="1" s="19"/>
+    <row r="501" ht="15.75" customHeight="1" s="19"/>
+    <row r="502" ht="15.75" customHeight="1" s="19"/>
+    <row r="503" ht="15.75" customHeight="1" s="19"/>
+    <row r="504" ht="15.75" customHeight="1" s="19"/>
+    <row r="505" ht="15.75" customHeight="1" s="19"/>
+    <row r="506" ht="15.75" customHeight="1" s="19"/>
+    <row r="507" ht="15.75" customHeight="1" s="19"/>
+    <row r="508" ht="15.75" customHeight="1" s="19"/>
+    <row r="509" ht="15.75" customHeight="1" s="19"/>
+    <row r="510" ht="15.75" customHeight="1" s="19"/>
+    <row r="511" ht="15.75" customHeight="1" s="19"/>
+    <row r="512" ht="15.75" customHeight="1" s="19"/>
+    <row r="513" ht="15.75" customHeight="1" s="19"/>
+    <row r="514" ht="15.75" customHeight="1" s="19"/>
+    <row r="515" ht="15.75" customHeight="1" s="19"/>
+    <row r="516" ht="15.75" customHeight="1" s="19"/>
+    <row r="517" ht="15.75" customHeight="1" s="19"/>
+    <row r="518" ht="15.75" customHeight="1" s="19"/>
+    <row r="519" ht="15.75" customHeight="1" s="19"/>
+    <row r="520" ht="15.75" customHeight="1" s="19"/>
+    <row r="521" ht="15.75" customHeight="1" s="19"/>
+    <row r="522" ht="15.75" customHeight="1" s="19"/>
+    <row r="523" ht="15.75" customHeight="1" s="19"/>
+    <row r="524" ht="15.75" customHeight="1" s="19"/>
+    <row r="525" ht="15.75" customHeight="1" s="19"/>
+    <row r="526" ht="15.75" customHeight="1" s="19"/>
+    <row r="527" ht="15.75" customHeight="1" s="19"/>
+    <row r="528" ht="15.75" customHeight="1" s="19"/>
+    <row r="529" ht="15.75" customHeight="1" s="19"/>
+    <row r="530" ht="15.75" customHeight="1" s="19"/>
+    <row r="531" ht="15.75" customHeight="1" s="19"/>
+    <row r="532" ht="15.75" customHeight="1" s="19"/>
+    <row r="533" ht="15.75" customHeight="1" s="19"/>
+    <row r="534" ht="15.75" customHeight="1" s="19"/>
+    <row r="535" ht="15.75" customHeight="1" s="19"/>
+    <row r="536" ht="15.75" customHeight="1" s="19"/>
+    <row r="537" ht="15.75" customHeight="1" s="19"/>
+    <row r="538" ht="15.75" customHeight="1" s="19"/>
+    <row r="539" ht="15.75" customHeight="1" s="19"/>
+    <row r="540" ht="15.75" customHeight="1" s="19"/>
+    <row r="541" ht="15.75" customHeight="1" s="19"/>
+    <row r="542" ht="15.75" customHeight="1" s="19"/>
+    <row r="543" ht="15.75" customHeight="1" s="19"/>
+    <row r="544" ht="15.75" customHeight="1" s="19"/>
+    <row r="545" ht="15.75" customHeight="1" s="19"/>
+    <row r="546" ht="15.75" customHeight="1" s="19"/>
+    <row r="547" ht="15.75" customHeight="1" s="19"/>
+    <row r="548" ht="15.75" customHeight="1" s="19"/>
+    <row r="549" ht="15.75" customHeight="1" s="19"/>
+    <row r="550" ht="15.75" customHeight="1" s="19"/>
+    <row r="551" ht="15.75" customHeight="1" s="19"/>
+    <row r="552" ht="15.75" customHeight="1" s="19"/>
+    <row r="553" ht="15.75" customHeight="1" s="19"/>
+    <row r="554" ht="15.75" customHeight="1" s="19"/>
+    <row r="555" ht="15.75" customHeight="1" s="19"/>
+    <row r="556" ht="15.75" customHeight="1" s="19"/>
+    <row r="557" ht="15.75" customHeight="1" s="19"/>
+    <row r="558" ht="15.75" customHeight="1" s="19"/>
+    <row r="559" ht="15.75" customHeight="1" s="19"/>
+    <row r="560" ht="15.75" customHeight="1" s="19"/>
+    <row r="561" ht="15.75" customHeight="1" s="19"/>
+    <row r="562" ht="15.75" customHeight="1" s="19"/>
+    <row r="563" ht="15.75" customHeight="1" s="19"/>
+    <row r="564" ht="15.75" customHeight="1" s="19"/>
+    <row r="565" ht="15.75" customHeight="1" s="19"/>
+    <row r="566" ht="15.75" customHeight="1" s="19"/>
+    <row r="567" ht="15.75" customHeight="1" s="19"/>
+    <row r="568" ht="15.75" customHeight="1" s="19"/>
+    <row r="569" ht="15.75" customHeight="1" s="19"/>
+    <row r="570" ht="15.75" customHeight="1" s="19"/>
+    <row r="571" ht="15.75" customHeight="1" s="19"/>
+    <row r="572" ht="15.75" customHeight="1" s="19"/>
+    <row r="573" ht="15.75" customHeight="1" s="19"/>
+    <row r="574" ht="15.75" customHeight="1" s="19"/>
+    <row r="575" ht="15.75" customHeight="1" s="19"/>
+    <row r="576" ht="15.75" customHeight="1" s="19"/>
+    <row r="577" ht="15.75" customHeight="1" s="19"/>
+    <row r="578" ht="15.75" customHeight="1" s="19"/>
+    <row r="579" ht="15.75" customHeight="1" s="19"/>
+    <row r="580" ht="15.75" customHeight="1" s="19"/>
+    <row r="581" ht="15.75" customHeight="1" s="19"/>
+    <row r="582" ht="15.75" customHeight="1" s="19"/>
+    <row r="583" ht="15.75" customHeight="1" s="19"/>
+    <row r="584" ht="15.75" customHeight="1" s="19"/>
+    <row r="585" ht="15.75" customHeight="1" s="19"/>
+    <row r="586" ht="15.75" customHeight="1" s="19"/>
+    <row r="587" ht="15.75" customHeight="1" s="19"/>
+    <row r="588" ht="15.75" customHeight="1" s="19"/>
+    <row r="589" ht="15.75" customHeight="1" s="19"/>
+    <row r="590" ht="15.75" customHeight="1" s="19"/>
+    <row r="591" ht="15.75" customHeight="1" s="19"/>
+    <row r="592" ht="15.75" customHeight="1" s="19"/>
+    <row r="593" ht="15.75" customHeight="1" s="19"/>
+    <row r="594" ht="15.75" customHeight="1" s="19"/>
+    <row r="595" ht="15.75" customHeight="1" s="19"/>
+    <row r="596" ht="15.75" customHeight="1" s="19"/>
+    <row r="597" ht="15.75" customHeight="1" s="19"/>
+    <row r="598" ht="15.75" customHeight="1" s="19"/>
+    <row r="599" ht="15.75" customHeight="1" s="19"/>
+    <row r="600" ht="15.75" customHeight="1" s="19"/>
+    <row r="601" ht="15.75" customHeight="1" s="19"/>
+    <row r="602" ht="15.75" customHeight="1" s="19"/>
+    <row r="603" ht="15.75" customHeight="1" s="19"/>
+    <row r="604" ht="15.75" customHeight="1" s="19"/>
+    <row r="605" ht="15.75" customHeight="1" s="19"/>
+    <row r="606" ht="15.75" customHeight="1" s="19"/>
+    <row r="607" ht="15.75" customHeight="1" s="19"/>
+    <row r="608" ht="15.75" customHeight="1" s="19"/>
+    <row r="609" ht="15.75" customHeight="1" s="19"/>
+    <row r="610" ht="15.75" customHeight="1" s="19"/>
+    <row r="611" ht="15.75" customHeight="1" s="19"/>
+    <row r="612" ht="15.75" customHeight="1" s="19"/>
+    <row r="613" ht="15.75" customHeight="1" s="19"/>
+    <row r="614" ht="15.75" customHeight="1" s="19"/>
+    <row r="615" ht="15.75" customHeight="1" s="19"/>
+    <row r="616" ht="15.75" customHeight="1" s="19"/>
+    <row r="617" ht="15.75" customHeight="1" s="19"/>
+    <row r="618" ht="15.75" customHeight="1" s="19"/>
+    <row r="619" ht="15.75" customHeight="1" s="19"/>
+    <row r="620" ht="15.75" customHeight="1" s="19"/>
+    <row r="621" ht="15.75" customHeight="1" s="19"/>
+    <row r="622" ht="15.75" customHeight="1" s="19"/>
+    <row r="623" ht="15.75" customHeight="1" s="19"/>
+    <row r="624" ht="15.75" customHeight="1" s="19"/>
+    <row r="625" ht="15.75" customHeight="1" s="19"/>
+    <row r="626" ht="15.75" customHeight="1" s="19"/>
+    <row r="627" ht="15.75" customHeight="1" s="19"/>
+    <row r="628" ht="15.75" customHeight="1" s="19"/>
+    <row r="629" ht="15.75" customHeight="1" s="19"/>
+    <row r="630" ht="15.75" customHeight="1" s="19"/>
+    <row r="631" ht="15.75" customHeight="1" s="19"/>
+    <row r="632" ht="15.75" customHeight="1" s="19"/>
+    <row r="633" ht="15.75" customHeight="1" s="19"/>
+    <row r="634" ht="15.75" customHeight="1" s="19"/>
+    <row r="635" ht="15.75" customHeight="1" s="19"/>
+    <row r="636" ht="15.75" customHeight="1" s="19"/>
+    <row r="637" ht="15.75" customHeight="1" s="19"/>
+    <row r="638" ht="15.75" customHeight="1" s="19"/>
+    <row r="639" ht="15.75" customHeight="1" s="19"/>
+    <row r="640" ht="15.75" customHeight="1" s="19"/>
+    <row r="641" ht="15.75" customHeight="1" s="19"/>
+    <row r="642" ht="15.75" customHeight="1" s="19"/>
+    <row r="643" ht="15.75" customHeight="1" s="19"/>
+    <row r="644" ht="15.75" customHeight="1" s="19"/>
+    <row r="645" ht="15.75" customHeight="1" s="19"/>
+    <row r="646" ht="15.75" customHeight="1" s="19"/>
+    <row r="647" ht="15.75" customHeight="1" s="19"/>
+    <row r="648" ht="15.75" customHeight="1" s="19"/>
+    <row r="649" ht="15.75" customHeight="1" s="19"/>
+    <row r="650" ht="15.75" customHeight="1" s="19"/>
+    <row r="651" ht="15.75" customHeight="1" s="19"/>
+    <row r="652" ht="15.75" customHeight="1" s="19"/>
+    <row r="653" ht="15.75" customHeight="1" s="19"/>
+    <row r="654" ht="15.75" customHeight="1" s="19"/>
+    <row r="655" ht="15.75" customHeight="1" s="19"/>
+    <row r="656" ht="15.75" customHeight="1" s="19"/>
+    <row r="657" ht="15.75" customHeight="1" s="19"/>
+    <row r="658" ht="15.75" customHeight="1" s="19"/>
+    <row r="659" ht="15.75" customHeight="1" s="19"/>
+    <row r="660" ht="15.75" customHeight="1" s="19"/>
+    <row r="661" ht="15.75" customHeight="1" s="19"/>
+    <row r="662" ht="15.75" customHeight="1" s="19"/>
+    <row r="663" ht="15.75" customHeight="1" s="19"/>
+    <row r="664" ht="15.75" customHeight="1" s="19"/>
+    <row r="665" ht="15.75" customHeight="1" s="19"/>
+    <row r="666" ht="15.75" customHeight="1" s="19"/>
+    <row r="667" ht="15.75" customHeight="1" s="19"/>
+    <row r="668" ht="15.75" customHeight="1" s="19"/>
+    <row r="669" ht="15.75" customHeight="1" s="19"/>
+    <row r="670" ht="15.75" customHeight="1" s="19"/>
+    <row r="671" ht="15.75" customHeight="1" s="19"/>
+    <row r="672" ht="15.75" customHeight="1" s="19"/>
+    <row r="673" ht="15.75" customHeight="1" s="19"/>
+    <row r="674" ht="15.75" customHeight="1" s="19"/>
+    <row r="675" ht="15.75" customHeight="1" s="19"/>
+    <row r="676" ht="15.75" customHeight="1" s="19"/>
+    <row r="677" ht="15.75" customHeight="1" s="19"/>
+    <row r="678" ht="15.75" customHeight="1" s="19"/>
+    <row r="679" ht="15.75" customHeight="1" s="19"/>
+    <row r="680" ht="15.75" customHeight="1" s="19"/>
+    <row r="681" ht="15.75" customHeight="1" s="19"/>
+    <row r="682" ht="15.75" customHeight="1" s="19"/>
+    <row r="683" ht="15.75" customHeight="1" s="19"/>
+    <row r="684" ht="15.75" customHeight="1" s="19"/>
+    <row r="685" ht="15.75" customHeight="1" s="19"/>
+    <row r="686" ht="15.75" customHeight="1" s="19"/>
+    <row r="687" ht="15.75" customHeight="1" s="19"/>
+    <row r="688" ht="15.75" customHeight="1" s="19"/>
+    <row r="689" ht="15.75" customHeight="1" s="19"/>
+    <row r="690" ht="15.75" customHeight="1" s="19"/>
+    <row r="691" ht="15.75" customHeight="1" s="19"/>
+    <row r="692" ht="15.75" customHeight="1" s="19"/>
+    <row r="693" ht="15.75" customHeight="1" s="19"/>
+    <row r="694" ht="15.75" customHeight="1" s="19"/>
+    <row r="695" ht="15.75" customHeight="1" s="19"/>
+    <row r="696" ht="15.75" customHeight="1" s="19"/>
+    <row r="697" ht="15.75" customHeight="1" s="19"/>
+    <row r="698" ht="15.75" customHeight="1" s="19"/>
+    <row r="699" ht="15.75" customHeight="1" s="19"/>
+    <row r="700" ht="15.75" customHeight="1" s="19"/>
+    <row r="701" ht="15.75" customHeight="1" s="19"/>
+    <row r="702" ht="15.75" customHeight="1" s="19"/>
+    <row r="703" ht="15.75" customHeight="1" s="19"/>
+    <row r="704" ht="15.75" customHeight="1" s="19"/>
+    <row r="705" ht="15.75" customHeight="1" s="19"/>
+    <row r="706" ht="15.75" customHeight="1" s="19"/>
+    <row r="707" ht="15.75" customHeight="1" s="19"/>
+    <row r="708" ht="15.75" customHeight="1" s="19"/>
+    <row r="709" ht="15.75" customHeight="1" s="19"/>
+    <row r="710" ht="15.75" customHeight="1" s="19"/>
+    <row r="711" ht="15.75" customHeight="1" s="19"/>
+    <row r="712" ht="15.75" customHeight="1" s="19"/>
+    <row r="713" ht="15.75" customHeight="1" s="19"/>
+    <row r="714" ht="15.75" customHeight="1" s="19"/>
+    <row r="715" ht="15.75" customHeight="1" s="19"/>
+    <row r="716" ht="15.75" customHeight="1" s="19"/>
+    <row r="717" ht="15.75" customHeight="1" s="19"/>
+    <row r="718" ht="15.75" customHeight="1" s="19"/>
+    <row r="719" ht="15.75" customHeight="1" s="19"/>
+    <row r="720" ht="15.75" customHeight="1" s="19"/>
+    <row r="721" ht="15.75" customHeight="1" s="19"/>
+    <row r="722" ht="15.75" customHeight="1" s="19"/>
+    <row r="723" ht="15.75" customHeight="1" s="19"/>
+    <row r="724" ht="15.75" customHeight="1" s="19"/>
+    <row r="725" ht="15.75" customHeight="1" s="19"/>
+    <row r="726" ht="15.75" customHeight="1" s="19"/>
+    <row r="727" ht="15.75" customHeight="1" s="19"/>
+    <row r="728" ht="15.75" customHeight="1" s="19"/>
+    <row r="729" ht="15.75" customHeight="1" s="19"/>
+    <row r="730" ht="15.75" customHeight="1" s="19"/>
+    <row r="731" ht="15.75" customHeight="1" s="19"/>
+    <row r="732" ht="15.75" customHeight="1" s="19"/>
+    <row r="733" ht="15.75" customHeight="1" s="19"/>
+    <row r="734" ht="15.75" customHeight="1" s="19"/>
+    <row r="735" ht="15.75" customHeight="1" s="19"/>
+    <row r="736" ht="15.75" customHeight="1" s="19"/>
+    <row r="737" ht="15.75" customHeight="1" s="19"/>
+    <row r="738" ht="15.75" customHeight="1" s="19"/>
+    <row r="739" ht="15.75" customHeight="1" s="19"/>
+    <row r="740" ht="15.75" customHeight="1" s="19"/>
+    <row r="741" ht="15.75" customHeight="1" s="19"/>
+    <row r="742" ht="15.75" customHeight="1" s="19"/>
+    <row r="743" ht="15.75" customHeight="1" s="19"/>
+    <row r="744" ht="15.75" customHeight="1" s="19"/>
+    <row r="745" ht="15.75" customHeight="1" s="19"/>
+    <row r="746" ht="15.75" customHeight="1" s="19"/>
+    <row r="747" ht="15.75" customHeight="1" s="19"/>
+    <row r="748" ht="15.75" customHeight="1" s="19"/>
+    <row r="749" ht="15.75" customHeight="1" s="19"/>
+    <row r="750" ht="15.75" customHeight="1" s="19"/>
+    <row r="751" ht="15.75" customHeight="1" s="19"/>
+    <row r="752" ht="15.75" customHeight="1" s="19"/>
+    <row r="753" ht="15.75" customHeight="1" s="19"/>
+    <row r="754" ht="15.75" customHeight="1" s="19"/>
+    <row r="755" ht="15.75" customHeight="1" s="19"/>
+    <row r="756" ht="15.75" customHeight="1" s="19"/>
+    <row r="757" ht="15.75" customHeight="1" s="19"/>
+    <row r="758" ht="15.75" customHeight="1" s="19"/>
+    <row r="759" ht="15.75" customHeight="1" s="19"/>
+    <row r="760" ht="15.75" customHeight="1" s="19"/>
+    <row r="761" ht="15.75" customHeight="1" s="19"/>
+    <row r="762" ht="15.75" customHeight="1" s="19"/>
+    <row r="763" ht="15.75" customHeight="1" s="19"/>
+    <row r="764" ht="15.75" customHeight="1" s="19"/>
+    <row r="765" ht="15.75" customHeight="1" s="19"/>
+    <row r="766" ht="15.75" customHeight="1" s="19"/>
+    <row r="767" ht="15.75" customHeight="1" s="19"/>
+    <row r="768" ht="15.75" customHeight="1" s="19"/>
+    <row r="769" ht="15.75" customHeight="1" s="19"/>
+    <row r="770" ht="15.75" customHeight="1" s="19"/>
+    <row r="771" ht="15.75" customHeight="1" s="19"/>
+    <row r="772" ht="15.75" customHeight="1" s="19"/>
+    <row r="773" ht="15.75" customHeight="1" s="19"/>
+    <row r="774" ht="15.75" customHeight="1" s="19"/>
+    <row r="775" ht="15.75" customHeight="1" s="19"/>
+    <row r="776" ht="15.75" customHeight="1" s="19"/>
+    <row r="777" ht="15.75" customHeight="1" s="19"/>
+    <row r="778" ht="15.75" customHeight="1" s="19"/>
+    <row r="779" ht="15.75" customHeight="1" s="19"/>
+    <row r="780" ht="15.75" customHeight="1" s="19"/>
+    <row r="781" ht="15.75" customHeight="1" s="19"/>
+    <row r="782" ht="15.75" customHeight="1" s="19"/>
+    <row r="783" ht="15.75" customHeight="1" s="19"/>
+    <row r="784" ht="15.75" customHeight="1" s="19"/>
+    <row r="785" ht="15.75" customHeight="1" s="19"/>
+    <row r="786" ht="15.75" customHeight="1" s="19"/>
+    <row r="787" ht="15.75" customHeight="1" s="19"/>
+    <row r="788" ht="15.75" customHeight="1" s="19"/>
+    <row r="789" ht="15.75" customHeight="1" s="19"/>
+    <row r="790" ht="15.75" customHeight="1" s="19"/>
+    <row r="791" ht="15.75" customHeight="1" s="19"/>
+    <row r="792" ht="15.75" customHeight="1" s="19"/>
+    <row r="793" ht="15.75" customHeight="1" s="19"/>
+    <row r="794" ht="15.75" customHeight="1" s="19"/>
+    <row r="795" ht="15.75" customHeight="1" s="19"/>
+    <row r="796" ht="15.75" customHeight="1" s="19"/>
+    <row r="797" ht="15.75" customHeight="1" s="19"/>
+    <row r="798" ht="15.75" customHeight="1" s="19"/>
+    <row r="799" ht="15.75" customHeight="1" s="19"/>
+    <row r="800" ht="15.75" customHeight="1" s="19"/>
+    <row r="801" ht="15.75" customHeight="1" s="19"/>
+    <row r="802" ht="15.75" customHeight="1" s="19"/>
+    <row r="803" ht="15.75" customHeight="1" s="19"/>
+    <row r="804" ht="15.75" customHeight="1" s="19"/>
+    <row r="805" ht="15.75" customHeight="1" s="19"/>
+    <row r="806" ht="15.75" customHeight="1" s="19"/>
+    <row r="807" ht="15.75" customHeight="1" s="19"/>
+    <row r="808" ht="15.75" customHeight="1" s="19"/>
+    <row r="809" ht="15.75" customHeight="1" s="19"/>
+    <row r="810" ht="15.75" customHeight="1" s="19"/>
+    <row r="811" ht="15.75" customHeight="1" s="19"/>
+    <row r="812" ht="15.75" customHeight="1" s="19"/>
+    <row r="813" ht="15.75" customHeight="1" s="19"/>
+    <row r="814" ht="15.75" customHeight="1" s="19"/>
+    <row r="815" ht="15.75" customHeight="1" s="19"/>
+    <row r="816" ht="15.75" customHeight="1" s="19"/>
+    <row r="817" ht="15.75" customHeight="1" s="19"/>
+    <row r="818" ht="15.75" customHeight="1" s="19"/>
+    <row r="819" ht="15.75" customHeight="1" s="19"/>
+    <row r="820" ht="15.75" customHeight="1" s="19"/>
+    <row r="821" ht="15.75" customHeight="1" s="19"/>
+    <row r="822" ht="15.75" customHeight="1" s="19"/>
+    <row r="823" ht="15.75" customHeight="1" s="19"/>
+    <row r="824" ht="15.75" customHeight="1" s="19"/>
+    <row r="825" ht="15.75" customHeight="1" s="19"/>
+    <row r="826" ht="15.75" customHeight="1" s="19"/>
+    <row r="827" ht="15.75" customHeight="1" s="19"/>
+    <row r="828" ht="15.75" customHeight="1" s="19"/>
+    <row r="829" ht="15.75" customHeight="1" s="19"/>
+    <row r="830" ht="15.75" customHeight="1" s="19"/>
+    <row r="831" ht="15.75" customHeight="1" s="19"/>
+    <row r="832" ht="15.75" customHeight="1" s="19"/>
+    <row r="833" ht="15.75" customHeight="1" s="19"/>
+    <row r="834" ht="15.75" customHeight="1" s="19"/>
+    <row r="835" ht="15.75" customHeight="1" s="19"/>
+    <row r="836" ht="15.75" customHeight="1" s="19"/>
+    <row r="837" ht="15.75" customHeight="1" s="19"/>
+    <row r="838" ht="15.75" customHeight="1" s="19"/>
+    <row r="839" ht="15.75" customHeight="1" s="19"/>
+    <row r="840" ht="15.75" customHeight="1" s="19"/>
+    <row r="841" ht="15.75" customHeight="1" s="19"/>
+    <row r="842" ht="15.75" customHeight="1" s="19"/>
+    <row r="843" ht="15.75" customHeight="1" s="19"/>
+    <row r="844" ht="15.75" customHeight="1" s="19"/>
+    <row r="845" ht="15.75" customHeight="1" s="19"/>
+    <row r="846" ht="15.75" customHeight="1" s="19"/>
+    <row r="847" ht="15.75" customHeight="1" s="19"/>
+    <row r="848" ht="15.75" customHeight="1" s="19"/>
+    <row r="849" ht="15.75" customHeight="1" s="19"/>
+    <row r="850" ht="15.75" customHeight="1" s="19"/>
+    <row r="851" ht="15.75" customHeight="1" s="19"/>
+    <row r="852" ht="15.75" customHeight="1" s="19"/>
+    <row r="853" ht="15.75" customHeight="1" s="19"/>
+    <row r="854" ht="15.75" customHeight="1" s="19"/>
+    <row r="855" ht="15.75" customHeight="1" s="19"/>
+    <row r="856" ht="15.75" customHeight="1" s="19"/>
+    <row r="857" ht="15.75" customHeight="1" s="19"/>
+    <row r="858" ht="15.75" customHeight="1" s="19"/>
+    <row r="859" ht="15.75" customHeight="1" s="19"/>
+    <row r="860" ht="15.75" customHeight="1" s="19"/>
+    <row r="861" ht="15.75" customHeight="1" s="19"/>
+    <row r="862" ht="15.75" customHeight="1" s="19"/>
+    <row r="863" ht="15.75" customHeight="1" s="19"/>
+    <row r="864" ht="15.75" customHeight="1" s="19"/>
+    <row r="865" ht="15.75" customHeight="1" s="19"/>
+    <row r="866" ht="15.75" customHeight="1" s="19"/>
+    <row r="867" ht="15.75" customHeight="1" s="19"/>
+    <row r="868" ht="15.75" customHeight="1" s="19"/>
+    <row r="869" ht="15.75" customHeight="1" s="19"/>
+    <row r="870" ht="15.75" customHeight="1" s="19"/>
+    <row r="871" ht="15.75" customHeight="1" s="19"/>
+    <row r="872" ht="15.75" customHeight="1" s="19"/>
+    <row r="873" ht="15.75" customHeight="1" s="19"/>
+    <row r="874" ht="15.75" customHeight="1" s="19"/>
+    <row r="875" ht="15.75" customHeight="1" s="19"/>
+    <row r="876" ht="15.75" customHeight="1" s="19"/>
+    <row r="877" ht="15.75" customHeight="1" s="19"/>
+    <row r="878" ht="15.75" customHeight="1" s="19"/>
+    <row r="879" ht="15.75" customHeight="1" s="19"/>
+    <row r="880" ht="15.75" customHeight="1" s="19"/>
+    <row r="881" ht="15.75" customHeight="1" s="19"/>
+    <row r="882" ht="15.75" customHeight="1" s="19"/>
+    <row r="883" ht="15.75" customHeight="1" s="19"/>
+    <row r="884" ht="15.75" customHeight="1" s="19"/>
+    <row r="885" ht="15.75" customHeight="1" s="19"/>
+    <row r="886" ht="15.75" customHeight="1" s="19"/>
+    <row r="887" ht="15.75" customHeight="1" s="19"/>
+    <row r="888" ht="15.75" customHeight="1" s="19"/>
+    <row r="889" ht="15.75" customHeight="1" s="19"/>
+    <row r="890" ht="15.75" customHeight="1" s="19"/>
+    <row r="891" ht="15.75" customHeight="1" s="19"/>
+    <row r="892" ht="15.75" customHeight="1" s="19"/>
+    <row r="893" ht="15.75" customHeight="1" s="19"/>
+    <row r="894" ht="15.75" customHeight="1" s="19"/>
+    <row r="895" ht="15.75" customHeight="1" s="19"/>
+    <row r="896" ht="15.75" customHeight="1" s="19"/>
+    <row r="897" ht="15.75" customHeight="1" s="19"/>
+    <row r="898" ht="15.75" customHeight="1" s="19"/>
+    <row r="899" ht="15.75" customHeight="1" s="19"/>
+    <row r="900" ht="15.75" customHeight="1" s="19"/>
+    <row r="901" ht="15.75" customHeight="1" s="19"/>
+    <row r="902" ht="15.75" customHeight="1" s="19"/>
+    <row r="903" ht="15.75" customHeight="1" s="19"/>
+    <row r="904" ht="15.75" customHeight="1" s="19"/>
+    <row r="905" ht="15.75" customHeight="1" s="19"/>
+    <row r="906" ht="15.75" customHeight="1" s="19"/>
+    <row r="907" ht="15.75" customHeight="1" s="19"/>
+    <row r="908" ht="15.75" customHeight="1" s="19"/>
+    <row r="909" ht="15.75" customHeight="1" s="19"/>
+    <row r="910" ht="15.75" customHeight="1" s="19"/>
+    <row r="911" ht="15.75" customHeight="1" s="19"/>
+    <row r="912" ht="15.75" customHeight="1" s="19"/>
+    <row r="913" ht="15.75" customHeight="1" s="19"/>
+    <row r="914" ht="15.75" customHeight="1" s="19"/>
+    <row r="915" ht="15.75" customHeight="1" s="19"/>
+    <row r="916" ht="15.75" customHeight="1" s="19"/>
+    <row r="917" ht="15.75" customHeight="1" s="19"/>
+    <row r="918" ht="15.75" customHeight="1" s="19"/>
+    <row r="919" ht="15.75" customHeight="1" s="19"/>
+    <row r="920" ht="15.75" customHeight="1" s="19"/>
+    <row r="921" ht="15.75" customHeight="1" s="19"/>
+    <row r="922" ht="15.75" customHeight="1" s="19"/>
+    <row r="923" ht="15.75" customHeight="1" s="19"/>
+    <row r="924" ht="15.75" customHeight="1" s="19"/>
+    <row r="925" ht="15.75" customHeight="1" s="19"/>
+    <row r="926" ht="15.75" customHeight="1" s="19"/>
+    <row r="927" ht="15.75" customHeight="1" s="19"/>
+    <row r="928" ht="15.75" customHeight="1" s="19"/>
+    <row r="929" ht="15.75" customHeight="1" s="19"/>
+    <row r="930" ht="15.75" customHeight="1" s="19"/>
+    <row r="931" ht="15.75" customHeight="1" s="19"/>
+    <row r="932" ht="15.75" customHeight="1" s="19"/>
+    <row r="933" ht="15.75" customHeight="1" s="19"/>
+    <row r="934" ht="15.75" customHeight="1" s="19"/>
+    <row r="935" ht="15.75" customHeight="1" s="19"/>
+    <row r="936" ht="15.75" customHeight="1" s="19"/>
+    <row r="937" ht="15.75" customHeight="1" s="19"/>
+    <row r="938" ht="15.75" customHeight="1" s="19"/>
+    <row r="939" ht="15.75" customHeight="1" s="19"/>
+    <row r="940" ht="15.75" customHeight="1" s="19"/>
+    <row r="941" ht="15.75" customHeight="1" s="19"/>
+    <row r="942" ht="15.75" customHeight="1" s="19"/>
+    <row r="943" ht="15.75" customHeight="1" s="19"/>
+    <row r="944" ht="15.75" customHeight="1" s="19"/>
+    <row r="945" ht="15.75" customHeight="1" s="19"/>
+    <row r="946" ht="15.75" customHeight="1" s="19"/>
+    <row r="947" ht="15.75" customHeight="1" s="19"/>
+    <row r="948" ht="15.75" customHeight="1" s="19"/>
+    <row r="949" ht="15.75" customHeight="1" s="19"/>
+    <row r="950" ht="15.75" customHeight="1" s="19"/>
+    <row r="951" ht="15.75" customHeight="1" s="19"/>
+    <row r="952" ht="15.75" customHeight="1" s="19"/>
+    <row r="953" ht="15.75" customHeight="1" s="19"/>
+    <row r="954" ht="15.75" customHeight="1" s="19"/>
+    <row r="955" ht="15.75" customHeight="1" s="19"/>
+    <row r="956" ht="15.75" customHeight="1" s="19"/>
+    <row r="957" ht="15.75" customHeight="1" s="19"/>
+    <row r="958" ht="15.75" customHeight="1" s="19"/>
+    <row r="959" ht="15.75" customHeight="1" s="19"/>
+    <row r="960" ht="15.75" customHeight="1" s="19"/>
+    <row r="961" ht="15.75" customHeight="1" s="19"/>
+    <row r="962" ht="15.75" customHeight="1" s="19"/>
+    <row r="963" ht="15.75" customHeight="1" s="19"/>
+    <row r="964" ht="15.75" customHeight="1" s="19"/>
+    <row r="965" ht="15.75" customHeight="1" s="19"/>
+    <row r="966" ht="15.75" customHeight="1" s="19"/>
+    <row r="967" ht="15.75" customHeight="1" s="19"/>
+    <row r="968" ht="15.75" customHeight="1" s="19"/>
+    <row r="969" ht="15.75" customHeight="1" s="19"/>
+    <row r="970" ht="15.75" customHeight="1" s="19"/>
+    <row r="971" ht="15.75" customHeight="1" s="19"/>
+    <row r="972" ht="15.75" customHeight="1" s="19"/>
+    <row r="973" ht="15.75" customHeight="1" s="19"/>
+    <row r="974" ht="15.75" customHeight="1" s="19"/>
+    <row r="975" ht="15.75" customHeight="1" s="19"/>
+    <row r="976" ht="15.75" customHeight="1" s="19"/>
+    <row r="977" ht="15.75" customHeight="1" s="19"/>
+    <row r="978" ht="15.75" customHeight="1" s="19"/>
+    <row r="979" ht="15.75" customHeight="1" s="19"/>
+    <row r="980" ht="15.75" customHeight="1" s="19"/>
+    <row r="981" ht="15.75" customHeight="1" s="19"/>
+    <row r="982" ht="15.75" customHeight="1" s="19"/>
+    <row r="983" ht="15.75" customHeight="1" s="19"/>
+    <row r="984" ht="15.75" customHeight="1" s="19"/>
+    <row r="985" ht="15.75" customHeight="1" s="19"/>
+    <row r="986" ht="15.75" customHeight="1" s="19"/>
+    <row r="987" ht="15.75" customHeight="1" s="19"/>
+    <row r="988" ht="15.75" customHeight="1" s="19"/>
+    <row r="989" ht="15.75" customHeight="1" s="19"/>
+    <row r="990" ht="15.75" customHeight="1" s="19"/>
+    <row r="991" ht="15.75" customHeight="1" s="19"/>
+    <row r="992" ht="15.75" customHeight="1" s="19"/>
+    <row r="993" ht="15.75" customHeight="1" s="19"/>
+    <row r="994" ht="15.75" customHeight="1" s="19"/>
+    <row r="995" ht="15.75" customHeight="1" s="19"/>
+    <row r="996" ht="15.75" customHeight="1" s="19"/>
+    <row r="997" ht="15.75" customHeight="1" s="19"/>
+    <row r="998" ht="15.75" customHeight="1" s="19"/>
+    <row r="999" ht="15.75" customHeight="1" s="19"/>
+    <row r="1000" ht="15.75" customHeight="1" s="19"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="19" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="19">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="19">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+Nothing is saved in this case.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="98.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Click 'Edit event information'
@@ -17467,7 +17606,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM62 Harbour Leadership Summit | Registration closes: 15 Mar 2027, 09:00 | Proposed: 14 Mar 2027, 09:00–17:00</t>
         </is>
@@ -17479,7 +17618,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved and no dialog appears. 'Registration closes after this start time. Change the registration period first.' is shown in red under 'Starts at'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time'.
 Step 6: The event page shows 'When' '17 Mar 2027, 09:00–17:00'.</t>
@@ -17492,7 +17631,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17524,7 +17663,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved and no dialog appears. 'Registration closes after this start time. Change the registration period first.' is shown in red under 'Starts at'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time'.
 Step 6: The event page shows 'When' '17 Mar 2027, 09:00–17:00'.</t>
@@ -17561,7 +17700,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17591,7 +17730,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved and no dialog appears. 'Registration closes after this start time. Change the registration period first.' is shown in red under 'Starts at'. The amber 'These changes affect existing arrangements' alert is also shown, listing 'Date and time'.
 Step 6: The event page shows 'When' '17 Mar 2027, 09:00–17:00'.</t>
@@ -17628,7 +17767,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -18657,9 +18796,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC02</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC01</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18808,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
@@ -18677,53 +18816,43 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="152.25" customHeight="1" s="19">
+    <row r="4" ht="57.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Click 'Edit event information'
-3. Change 'Description' to 'Updated programme with a panel discussion'
-4. Change 'Starts at' to 24 Mar 2027, 09:00
-5. Change 'Ends at' to 24 Mar 2027, 17:00
-6. Change 'Expected attendance' to 95
-7. Tick 'Hearing induction loop' under 'Accessibility needs'
-8. Click 'Cancel'
-9. Click 'Edit event information'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
+3. Click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning) | Description: Updated programme with a panel discussion | New start: 24 Mar 2027, 09:00 | New end: 24 Mar 2027, 17:00 | Expected attendance: 80 -&gt; 95 | Accessibility need: Hearing induction loop</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="314.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit | Status: Planning | When: 17 Mar 2027, 09:00–17:00 | Expected attendance: 80 | Layout: Theatre | Required facility: Fixed ceiling projector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="206.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
-Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: The alert still lists only 'Date and time'.
-Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
-Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
+Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
+Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18862,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18765,15 +18894,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
-Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: The alert still lists only 'Date and time'.
-Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
-Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
+Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
+Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
         </is>
       </c>
     </row>
@@ -18807,7 +18932,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18837,15 +18962,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
-Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: The alert still lists only 'Date and time'.
-Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
-Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and an 'Edit event information' button at the top of the page.
+Step 2: The 'Edit event information' page opens with the 'Planning' status badge. The form is filled in with the event's current information: Event name 'SPM62 Harbour Leadership Summit', Starts at 17 Mar 2027 09:00, Ends at 17 Mar 2027 17:00, Expected attendance 80, Preferred room layout 'Theatre', and 'Fixed ceiling projector' ticked under 'The venue must have'. There are no fields for Organiser, Company, Coordinator or Status, no Registration section, and no equipment rows: an info message reads 'Equipment is changed on the Equipment tab.' The buttons are 'Save changes' and 'Cancel'. No amber warning is shown.
+Step 3: The event page opens again with the 'Planning' status badge and the same details as in step 1.</t>
         </is>
       </c>
     </row>
@@ -18879,7 +19000,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -19908,43 +20029,43 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Bayu Energy Outlook' is back in its starting state.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="165.75" customHeight="1" s="19">
+Nothing is saved in this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Bayu Energy Outlook'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Click 'Edit event information'
-3. Change 'Purpose' to 'Brief clients on the 2027 regional energy outlook'
-4. Change 'Description' to 'Keynote, market briefing and Q&amp;A'
-5. Change 'Anything else about the space' to 'Reserve the front row for speakers'
-6. Click 'Save changes'
-7. Click 'Back to event'
-8. Click 'Edit event information'</t>
+3. Change 'Description' to 'Updated programme with a panel discussion'
+4. Change 'Starts at' to 24 Mar 2027, 09:00
+5. Change 'Ends at' to 24 Mar 2027, 17:00
+6. Change 'Expected attendance' to 95
+7. Tick 'Hearing induction loop' under 'Accessibility needs'
+8. Click 'Cancel'
+9. Click 'Edit event information'</t>
         </is>
       </c>
     </row>
@@ -19954,25 +20075,27 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Bayu Energy Outlook | Status: Approved | No venue booking, equipment or registrations | Purpose: Brief clients on the 2027 regional energy outlook | Description: Keynote, market briefing and Q&amp;A | Anything else about the space: Reserve the front row for speakers</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="192.75" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning) | Description: Updated programme with a panel discussion | New start: 24 Mar 2027, 09:00 | New end: 24 Mar 2027, 17:00 | Expected attendance: 80 -&gt; 95 | Accessibility need: Hearing induction loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="314.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge.
-Step 5: No amber warning has appeared at any point while editing.
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
-Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
+Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: The alert still lists only 'Date and time'.
+Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
+Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
         </is>
       </c>
     </row>
@@ -19982,7 +20105,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20014,13 +20137,15 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge.
-Step 5: No amber warning has appeared at any point while editing.
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
-Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
+Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: The alert still lists only 'Date and time'.
+Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
+Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20179,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20084,13 +20209,15 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge.
-Step 5: No amber warning has appeared at any point while editing.
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
-Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
-Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 3: No amber warning appears. A description change does not affect arrangements.
+Step 4: An amber alert 'These changes affect existing arrangements' appears above the 'Save changes' button, reading 'You've changed: Date and time. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: The alert still lists only 'Date and time'.
+Step 6: The alert now reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 7: The alert now reads 'You've changed: Date and time, Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 8: The event page opens with nothing changed: 'When' in the Details card shows '17 Mar 2027, 09:00–17:00' and 'Expected attendance' shows '80'. No 'Event information updated.' alert is shown.
+Step 9: The form shows the original values again (Starts at 17 Mar 2027 09:00, Expected attendance 80, 'Hearing induction loop' not ticked) and no amber alert.</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20251,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -21153,9 +21280,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC04</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC03</t>
         </is>
       </c>
     </row>
@@ -21165,42 +21292,43 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Anchorpoint Logistics Forum' is back in its starting state.
+Before: run `npm run fixtures:spm62` so 'SPM62 Bayu Energy Outlook' is back in its starting state.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
 After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="111.75" customHeight="1" s="19">
+    <row r="4" ht="165.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Anchorpoint Logistics Forum'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Bayu Energy Outlook'
 2. Click 'Edit event information'
-3. Change 'Starts at' to 25 May 2027, 09:00
-4. Change 'Ends at' to 25 May 2027, 12:00
-5. Change 'Expected attendance' to 70
+3. Change 'Purpose' to 'Brief clients on the 2027 regional energy outlook'
+4. Change 'Description' to 'Keynote, market briefing and Q&amp;A'
+5. Change 'Anything else about the space' to 'Reserve the front row for speakers'
 6. Click 'Save changes'
-7. Click 'Back to event'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="57.75" customHeight="1" s="19">
+7. Click 'Back to event'
+8. Click 'Edit event information'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Anchorpoint Logistics Forum | Status: Approved | When: 18 May 2027, 09:00–12:00 -&gt; 25 May 2027, 09:00–12:00 | Expected attendance: 50 -&gt; 70 | No venue booking, equipment or registrations</t>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Bayu Energy Outlook | Status: Approved | No venue booking, equipment or registrations | Purpose: Brief clients on the 2027 regional energy outlook | Description: Keynote, market briefing and Q&amp;A | Anything else about the space: Reserve the front row for speakers</t>
         </is>
       </c>
     </row>
@@ -21210,12 +21338,13 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
-Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
-Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge.
+Step 5: No amber warning has appeared at any point while editing.
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
+Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21354,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21257,12 +21386,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
-Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
-Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge.
+Step 5: No amber warning has appeared at any point while editing.
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
+Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
         </is>
       </c>
     </row>
@@ -21296,7 +21426,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21326,12 +21456,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
-Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
-Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge.
+Step 5: No amber warning has appeared at any point while editing.
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown.
+Step 7: The event page shows the subtitle 'Brief clients on the 2027 regional energy outlook' under the title, Description 'Keynote, market briefing and Q&amp;A' in the Details card, and Special requirements 'Reserve the front row for speakers' in the Venue requirements card. The status badge still reads 'Approved' (editing information does not begin planning).
+Step 8: The form shows the saved Purpose, Description and 'Anything else about the space' values.</t>
         </is>
       </c>
     </row>
@@ -21365,7 +21496,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -22394,71 +22525,69 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="179.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Harbour Leadership Summit' is back in its starting state.
+Before: run `npm run fixtures:spm62` so 'SPM62 Anchorpoint Logistics Forum' is back in its starting state.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-After: if you are running SPM-62-TC06 next, go straight to it - it checks this change as the organiser. Otherwise run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="125.25" customHeight="1" s="19">
+After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Anchorpoint Logistics Forum'
 2. Click 'Edit event information'
-3. Change 'Starts at' to 24 Mar 2027, 09:00
-4. Change 'Ends at' to 24 Mar 2027, 17:00
-5. Click 'Save changes'
-6. Click 'Back to event'
-7. Click the 'Venue' tab
-8. Click the 'Equipment' tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
+3. Change 'Starts at' to 25 May 2027, 09:00
+4. Change 'Ends at' to 25 May 2027, 12:00
+5. Change 'Expected attendance' to 70
+6. Click 'Save changes'
+7. Click 'Back to event'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit | Status: Planning | When: 17 Mar 2027, 09:00–17:00 -&gt; 24 Mar 2027, 09:00–17:00 | Approved booking: Orchard Seminar Room (ORC-SEM) on 17 Mar 2027 | Equipment: 4K Portable Projector x 2, Reserved | Registrations: 12 attendees registered</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="260.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Anchorpoint Logistics Forum | Status: Approved | When: 18 May 2027, 09:00–12:00 -&gt; 25 May 2027, 09:00–12:00 | Expected attendance: 50 -&gt; 70 | No venue booking, equipment or registrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="192.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
-Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
-Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
-Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
+Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
+Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22597,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22500,13 +22629,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
-Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
-Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
-Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
+Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
+Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
         </is>
       </c>
     </row>
@@ -22540,7 +22668,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22570,13 +22698,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
-Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
-Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
-Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Approved' status badge, 'When' 18 May 2027, 09:00–12:00 and 'Expected attendance' 50. The Venue row reads 'Not booked yet'.
+Step 5: The amber alert reads 'You've changed: Date and time, Expected attendance. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 6: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. No 'Flagged for review' alert is shown, because the event has no venue booking, equipment or registrations to flag.
+Step 7: The Details card shows 'When' '25 May 2027, 09:00–12:00' and 'Expected attendance' '70'. The status badge still reads 'Approved'.</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22737,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -23639,59 +23766,71 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="125.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="179.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC05 has just been run ('SPM62 Harbour Leadership Summit' moved to 24 Mar 2027 by Daniel Tan; its arrangements flagged for review).
-Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), Event Organiser of 'SPM62 Harbour Leadership Summit'.
-After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="19">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
+Before: run `npm run fixtures:spm62` so 'SPM62 Harbour Leadership Summit' is back in its starting state.
+Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+After: if you are running SPM-62-TC06 next, go straight to it - it checks this change as the organiser. Otherwise run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
+2. Click 'Edit event information'
+3. Change 'Starts at' to 24 Mar 2027, 09:00
+4. Change 'Ends at' to 24 Mar 2027, 17:00
+5. Click 'Save changes'
+6. Click 'Back to event'
+7. Click the 'Venue' tab
+8. Click the 'Equipment' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning) | Organiser: Evelyn Chen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit | Status: Planning | When: 17 Mar 2027, 09:00–17:00 -&gt; 24 Mar 2027, 09:00–17:00 | Approved booking: Orchard Seminar Room (ORC-SEM) on 17 Mar 2027 | Equipment: 4K Portable Projector x 2, Reserved | Registrations: 12 attendees registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="260.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
+Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
+Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
+Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23840,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -23733,9 +23872,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
+Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
+Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
+Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23912,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -23799,9 +23942,13 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge, 'When' 17 Mar 2027, 09:00–17:00, and Venue 'Orchard Seminar Room (ORC-SEM)'.
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists three lines: 'Venue booking: Orchard Seminar Room (ORC-SEM) – the date or time changed'; 'Equipment: 4K Portable Projector × 2 – the date or time changed'; 'Registrations: 12 attendees – the date or time changed'.
+Step 6: The Details card shows 'When' '24 Mar 2027, 09:00–17:00' and still shows Venue 'Orchard Seminar Room (ORC-SEM)'. The status badge still reads 'Planning'.
+Step 7: The booking for Orchard Seminar Room (ORC-SEM) is still shown on 17 Mar 2027 with the 'Approved' badge. It has not been moved to 24 Mar 2027 or cancelled.
+Step 8: '4K Portable Projector', quantity 2, is still listed with the 'Reserved' badge.</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23982,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -24864,67 +25011,59 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152.25" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-Before: run `npm run fixtures:spm62` so 'SPM62 Kirana Supplier Day' is back in its starting state.
-Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC05 has just been run ('SPM62 Harbour Leadership Summit' moved to 24 Mar 2027 by Daniel Tan; its arrangements flagged for review).
+Logged in as Evelyn Chen (evelyn.chen@straitsmedic.com / password123), Event Organiser of 'SPM62 Harbour Leadership Summit'.
 After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.25" customHeight="1" s="19">
+    <row r="4" ht="30.75" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Kirana Supplier Day'
-2. Click 'Edit event information'
-3. Change 'Expected attendance' to 90
-4. Tick 'Step-free access' under 'Accessibility needs'
-5. Click 'Save changes'
-6. Click 'Back to event'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="19">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'My Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Kirana Supplier Day | Status: Planning | Expected attendance: 60 -&gt; 90 | Accessibility need added: Step-free access | Approved booking: Changi Conference Centre (CBP-CONF) | Equipment: Handheld Wireless Mic x 4, Reserved | Registrations: 8 attendees registered</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="206.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning) | Organiser: Evelyn Chen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
-Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
         </is>
       </c>
     </row>
@@ -24934,7 +25073,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -24966,11 +25105,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
-Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25141,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -25034,11 +25171,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
-Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
-Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Planning' status badge and 'When' '24 Mar 2027, 09:00–17:00'. Venue still reads 'Orchard Seminar Room (ORC-SEM)'.</t>
         </is>
       </c>
     </row>
@@ -25072,7 +25207,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>
@@ -26101,69 +26236,67 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-62-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="138.75" customHeight="1" s="19">
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
-'SPM62 Straits Pharmacy Forum' is Confirmed (if SPM-62-TC09 has been run since the last reset, run `npm run fixtures:spm62` first).
+Before: run `npm run fixtures:spm62` so 'SPM62 Kirana Supplier Day' is back in its starting state.
 Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), the coordinator assigned to every 'SPM62 …' event.
-Nothing is saved in this case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="111.75" customHeight="1" s="19">
+After: run `npm run fixtures:spm62` so the next tester starts from the same state (never `npx prisma db seed`, which wipes everyone's data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.25" customHeight="1" s="19">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Straits Pharmacy Forum'
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>1. Click 'All Events' in the sidebar and open 'SPM62 Kirana Supplier Day'
 2. Click 'Edit event information'
-3. Change 'Starts at' to 16 Jun 2027, 09:00
-4. Change 'Ends at' to 16 Jun 2027, 17:00
+3. Change 'Expected attendance' to 90
+4. Tick 'Step-free access' under 'Accessibility needs'
 5. Click 'Save changes'
-6. Click 'Keep editing'
-7. Click 'Cancel'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="19">
+6. Click 'Back to event'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Straits Pharmacy Forum | Status: Confirmed | When: 9 Jun 2027, 09:00–17:00 | Proposed: 16 Jun 2027, 09:00–17:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="152.25" customHeight="1" s="19">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Kirana Supplier Day | Status: Planning | Expected attendance: 60 -&gt; 90 | Accessibility need added: Step-free access | Approved booking: Changi Conference Centre (CBP-CONF) | Equipment: Handheld Wireless Mic x 4, Reserved | Registrations: 8 attendees registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="206.25" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
-Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
-Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
+Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
         </is>
       </c>
     </row>
@@ -26173,7 +26306,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -26205,12 +26338,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
-Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
-Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
+Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
         </is>
       </c>
     </row>
@@ -26244,7 +26376,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -26274,12 +26406,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The event page shows the 'Confirmed' status badge and 'When' '9 Jun 2027, 09:00–17:00'.
-Step 5: A dialog 'Move this event back to Planning?' reads 'SPM62 Straits Pharmacy Forum is Confirmed. Saving these changes moves it back to Planning so it can be confirmed again.' with the buttons 'Keep editing' and 'Save and move to Planning'.
-Step 6: The dialog closes. The form still shows Starts at 16 Jun 2027 09:00 and the amber alert listing 'Date and time'.
-Step 7: The event page opens with the 'Confirmed' status badge and 'When' still '9 Jun 2027, 09:00–17:00'.</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Step 4: The amber alert reads 'You've changed: Expected attendance, Venue requirements. Any venue booking, equipment or registrations already arranged will be flagged for review, not changed.'
+Step 5: No dialog appears. The form is replaced by a green alert 'Event information updated.' and a 'Back to event' link. Below it, an amber alert 'Flagged for review' reads 'These were arranged for the event's earlier details and have not been changed.' and lists one line only: 'Venue booking: Changi Conference Centre (CBP-CONF) – the expected attendance changed; the venue requirements changed'. There is no Equipment line and no Registrations line.
+Step 6: The Details card shows 'Expected attendance' '90', the Venue requirements card lists 'Step-free access', and the status badge still reads 'Planning'.</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26444,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Kayal</t>
         </is>

--- a/docs/test-cases/SPM-62_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-62_Test_Cases.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -60,6 +60,9 @@
       <name val="Arial"/>
       <color theme="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -145,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -199,6 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1171,11 +1177,15 @@
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H19" s="23" t="n"/>
-      <c r="I19" s="23" t="n"/>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -12474,7 +12484,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
@@ -12482,33 +12492,40 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>SPM-62-TC16</t>
-        </is>
-      </c>
+      <c r="B2" s="9" t="n"/>
     </row>
     <row r="3" ht="98.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-62-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.25" customHeight="1" s="19">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm62` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM62 …' events, never anyone else's data).
 Logged in as Grace Lim (grace.lim@connectsphere.com / password123), Operations Manager.
@@ -12516,13 +12533,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="98.25" customHeight="1" s="19">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="5" ht="30.75" customHeight="1" s="19">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar and open 'SPM62 Harbour Leadership Summit'
 2. Note the event reference shown next to the title (it starts with EVT-)
@@ -12530,190 +12547,189 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="19">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Grace Lim, Operations Manager</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="84.75" customHeight="1" s="19">
       <c r="A6" s="10" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM62 Harbour Leadership Summit (Planning) | User: Grace Lim, Operations Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="19">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="19">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B9" s="18" t="n">
         <v>46300</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="15.75" customHeight="1" s="19">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="19">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B16" s="18" t="n">
         <v>46300</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="19">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="19">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="19">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="19">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Planning' status badge. There is no 'Edit event information' button.
 Step 3: The 'Edit event information' page shows a red alert 'You can't edit this event's information' reading 'Only the coordinator assigned to this event can change its information.' and a 'Back to event' button. No form fields are shown.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="15.75" customHeight="1" s="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="19">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Kayal</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="19">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B22" s="18" t="n">
         <v>46302</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="19"/>
     <row r="23" ht="15.75" customHeight="1" s="19"/>
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
@@ -13693,6 +13709,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
